--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_electronics_consumer_office.xlsx
@@ -588,115 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0814</v>
+        <v>0.111</v>
+      </c>
+      <c r="E2">
+        <v>0.5920000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.0376984126984127</v>
+        <v>-0.008004131164471986</v>
       </c>
       <c r="H2">
-        <v>-0.0376984126984127</v>
+        <v>-0.008004131164471986</v>
       </c>
       <c r="I2">
-        <v>-0.03117913832199546</v>
+        <v>-0.0004363542473534728</v>
       </c>
       <c r="J2">
-        <v>-0.03117913832199546</v>
+        <v>-0.0004363542473534728</v>
       </c>
       <c r="K2">
-        <v>-10.2</v>
+        <v>21.1</v>
       </c>
       <c r="L2">
-        <v>-0.02891156462585034</v>
+        <v>0.05447973147430932</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01604426002766252</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0.05497630331753554</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01604426002766252</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0.05497630331753554</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>26.6</v>
+        <v>33.2</v>
       </c>
       <c r="V2">
-        <v>0.5659574468085107</v>
+        <v>0.4591977869986169</v>
       </c>
       <c r="W2">
-        <v>-0.2015810276679842</v>
+        <v>0.501187648456057</v>
       </c>
       <c r="X2">
-        <v>0.1395850164092082</v>
+        <v>0.1389727051053957</v>
       </c>
       <c r="Y2">
-        <v>-0.3411660440771924</v>
+        <v>0.3622149433506613</v>
       </c>
       <c r="Z2">
-        <v>8.021828103683491</v>
+        <v>5.398661834402006</v>
       </c>
       <c r="AA2">
-        <v>-0.2501136880400182</v>
+        <v>-0.002355729021466406</v>
       </c>
       <c r="AB2">
-        <v>0.07979042884821327</v>
+        <v>0.1208449005671305</v>
       </c>
       <c r="AC2">
-        <v>-0.3299041168882314</v>
+        <v>-0.123200629588597</v>
       </c>
       <c r="AD2">
-        <v>60.2</v>
+        <v>22.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>60.2</v>
+        <v>22.4</v>
       </c>
       <c r="AG2">
-        <v>33.6</v>
+        <v>-10.8</v>
       </c>
       <c r="AH2">
-        <v>0.5615671641791045</v>
+        <v>0.2365364308342133</v>
       </c>
       <c r="AI2">
-        <v>0.5884652981427174</v>
+        <v>0.2448087431693989</v>
       </c>
       <c r="AJ2">
-        <v>0.4168734491315137</v>
+        <v>-0.1756097560975611</v>
       </c>
       <c r="AK2">
-        <v>0.4438573315719947</v>
+        <v>-0.1852487135506004</v>
       </c>
       <c r="AL2">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AM2">
-        <v>1.214</v>
+        <v>0.8960000000000001</v>
       </c>
       <c r="AN2">
-        <v>-22.88973384030419</v>
+        <v>4.435643564356435</v>
       </c>
       <c r="AO2">
-        <v>-8.396946564885496</v>
+        <v>-0.1508928571428571</v>
       </c>
       <c r="AP2">
-        <v>-12.77566539923954</v>
+        <v>-2.13861386138614</v>
       </c>
       <c r="AQ2">
-        <v>-9.060955518945635</v>
+        <v>-0.1886160714285714</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0814</v>
+        <v>0.111</v>
+      </c>
+      <c r="E3">
+        <v>0.5920000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.0376984126984127</v>
+        <v>-0.008004131164471986</v>
       </c>
       <c r="H3">
-        <v>-0.0376984126984127</v>
+        <v>-0.008004131164471986</v>
       </c>
       <c r="I3">
-        <v>-0.03117913832199546</v>
+        <v>-0.0004363542473534728</v>
       </c>
       <c r="J3">
-        <v>-0.03117913832199546</v>
+        <v>-0.0004363542473534728</v>
       </c>
       <c r="K3">
-        <v>-10.2</v>
+        <v>21.1</v>
       </c>
       <c r="L3">
-        <v>-0.02891156462585034</v>
+        <v>0.05447973147430932</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1.16</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01604426002766252</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.05497630331753554</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1.16</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.01604426002766252</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.05497630331753554</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>26.6</v>
+        <v>33.2</v>
       </c>
       <c r="V3">
-        <v>0.5659574468085107</v>
+        <v>0.4591977869986169</v>
       </c>
       <c r="W3">
-        <v>-0.2015810276679842</v>
+        <v>0.501187648456057</v>
       </c>
       <c r="X3">
-        <v>0.1395850164092082</v>
+        <v>0.1389727051053957</v>
       </c>
       <c r="Y3">
-        <v>-0.3411660440771924</v>
+        <v>0.3622149433506613</v>
       </c>
       <c r="Z3">
-        <v>8.021828103683491</v>
+        <v>5.398661834402006</v>
       </c>
       <c r="AA3">
-        <v>-0.2501136880400182</v>
+        <v>-0.002355729021466406</v>
       </c>
       <c r="AB3">
-        <v>0.07979042884821327</v>
+        <v>0.1208449005671305</v>
       </c>
       <c r="AC3">
-        <v>-0.3299041168882314</v>
+        <v>-0.123200629588597</v>
       </c>
       <c r="AD3">
-        <v>60.2</v>
+        <v>22.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>60.2</v>
+        <v>22.4</v>
       </c>
       <c r="AG3">
-        <v>33.6</v>
+        <v>-10.8</v>
       </c>
       <c r="AH3">
-        <v>0.5615671641791045</v>
+        <v>0.2365364308342133</v>
       </c>
       <c r="AI3">
-        <v>0.5884652981427174</v>
+        <v>0.2448087431693989</v>
       </c>
       <c r="AJ3">
-        <v>0.4168734491315137</v>
+        <v>-0.1756097560975611</v>
       </c>
       <c r="AK3">
-        <v>0.4438573315719947</v>
+        <v>-0.1852487135506004</v>
       </c>
       <c r="AL3">
-        <v>1.31</v>
+        <v>1.12</v>
       </c>
       <c r="AM3">
-        <v>1.214</v>
+        <v>0.8960000000000001</v>
       </c>
       <c r="AN3">
-        <v>-22.88973384030419</v>
+        <v>4.435643564356435</v>
       </c>
       <c r="AO3">
-        <v>-8.396946564885496</v>
+        <v>-0.1508928571428571</v>
       </c>
       <c r="AP3">
-        <v>-12.77566539923954</v>
+        <v>-2.13861386138614</v>
       </c>
       <c r="AQ3">
-        <v>-9.060955518945635</v>
+        <v>-0.1886160714285714</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_electronics_consumer_office.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_electronics_consumer_office.xlsx
@@ -1133,43 +1133,43 @@
         <v>88.1458966565349</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>193.010195663753</v>
       </c>
       <c r="G2">
         <v>0.174336283185841</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0881150442477876</v>
       </c>
       <c r="I2">
         <v>0.019785075826052</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>292.8</v>
       </c>
       <c r="L2">
-        <v>299.461112677377</v>
+        <v>296.378488930816</v>
       </c>
       <c r="M2">
         <v>223.51</v>
       </c>
       <c r="N2">
-        <v>224.261112677377</v>
+        <v>224.165588930816</v>
       </c>
       <c r="O2">
         <v>5.91</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.9871</v>
       </c>
       <c r="Q2">
         <v>0.102686654888903</v>
       </c>
       <c r="R2">
-        <v>0.102331777568172</v>
+        <v>0.102376777568172</v>
       </c>
       <c r="S2">
         <v>0.06373661666253411</v>
@@ -1191,13 +1191,13 @@
         <v>0.10347283906212</v>
       </c>
       <c r="X2">
-        <v>0.102331777568172</v>
+        <v>0.102902805624416</v>
       </c>
       <c r="Y2">
         <v>1.12415097971961</v>
       </c>
       <c r="Z2">
-        <v>1.10190956734593</v>
+        <v>1.11303996701609</v>
       </c>
       <c r="AA2">
         <v>5.91</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.102331777568172</v>
+        <v>0.102376777568172</v>
       </c>
       <c r="C2">
-        <v>299.4611126773765</v>
+        <v>296.3784889308162</v>
       </c>
       <c r="D2">
-        <v>224.2611126773766</v>
+        <v>224.1655889308162</v>
       </c>
       <c r="E2">
-        <v>-5.91</v>
+        <v>-2.9229</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.9871</v>
       </c>
       <c r="G2">
         <v>75.2</v>
@@ -1451,28 +1451,28 @@
         <v>29</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.15025113</v>
       </c>
       <c r="N2">
-        <v>29</v>
+        <v>28.84974887</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>29</v>
+        <v>28.84974887</v>
       </c>
       <c r="Q2">
-        <v>33.9</v>
+        <v>33.74974887</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.102331777568172</v>
+        <v>0.1029028056244161</v>
       </c>
       <c r="T2">
-        <v>1.101909567345926</v>
+        <v>1.113039967016087</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>193.0101956637531</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.102376777568172</v>
+        <v>0.102421777568172</v>
       </c>
       <c r="C3">
-        <v>296.3784889308162</v>
+        <v>293.2959465260544</v>
       </c>
       <c r="D3">
-        <v>224.1655889308162</v>
+        <v>224.0701465260543</v>
       </c>
       <c r="E3">
-        <v>-2.9229</v>
+        <v>0.06420000000000048</v>
       </c>
       <c r="F3">
-        <v>2.9871</v>
+        <v>5.974200000000001</v>
       </c>
       <c r="G3">
         <v>75.2</v>
@@ -1533,28 +1533,28 @@
         <v>29</v>
       </c>
       <c r="M3">
-        <v>0.15025113</v>
+        <v>0.30050226</v>
       </c>
       <c r="N3">
-        <v>28.84974887</v>
+        <v>28.69949774</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>28.84974887</v>
+        <v>28.69949774</v>
       </c>
       <c r="Q3">
-        <v>33.74974887</v>
+        <v>33.59949774</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1029028056244161</v>
+        <v>0.1034854873144612</v>
       </c>
       <c r="T3">
-        <v>1.113039967016087</v>
+        <v>1.124397517699924</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>193.0101956637531</v>
+        <v>96.50509783187653</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.102421777568172</v>
+        <v>0.102466777568172</v>
       </c>
       <c r="C4">
-        <v>293.2959465260544</v>
+        <v>290.2134853592372</v>
       </c>
       <c r="D4">
-        <v>224.0701465260543</v>
+        <v>223.9747853592372</v>
       </c>
       <c r="E4">
-        <v>0.06420000000000048</v>
+        <v>3.051300000000001</v>
       </c>
       <c r="F4">
-        <v>5.974200000000001</v>
+        <v>8.961300000000001</v>
       </c>
       <c r="G4">
         <v>75.2</v>
@@ -1615,28 +1615,28 @@
         <v>29</v>
       </c>
       <c r="M4">
-        <v>0.30050226</v>
+        <v>0.45075339</v>
       </c>
       <c r="N4">
-        <v>28.69949774</v>
+        <v>28.54924661</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>28.69949774</v>
+        <v>28.54924661</v>
       </c>
       <c r="Q4">
-        <v>33.59949774</v>
+        <v>33.44924661</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1034854873144612</v>
+        <v>0.1040801830599711</v>
       </c>
       <c r="T4">
-        <v>1.124397517699924</v>
+        <v>1.135989244686521</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>96.50509783187653</v>
+        <v>64.33673188791769</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.102466777568172</v>
+        <v>0.102511777568172</v>
       </c>
       <c r="C5">
-        <v>290.2134853592372</v>
+        <v>287.1311053266875</v>
       </c>
       <c r="D5">
-        <v>223.9747853592372</v>
+        <v>223.8795053266875</v>
       </c>
       <c r="E5">
-        <v>3.051300000000001</v>
+        <v>6.038400000000001</v>
       </c>
       <c r="F5">
-        <v>8.961300000000001</v>
+        <v>11.9484</v>
       </c>
       <c r="G5">
         <v>75.2</v>
@@ -1697,28 +1697,28 @@
         <v>29</v>
       </c>
       <c r="M5">
-        <v>0.45075339</v>
+        <v>0.60100452</v>
       </c>
       <c r="N5">
-        <v>28.54924661</v>
+        <v>28.39899548</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>28.54924661</v>
+        <v>28.39899548</v>
       </c>
       <c r="Q5">
-        <v>33.44924661</v>
+        <v>33.29899548</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1040801830599711</v>
+        <v>0.1046872683001791</v>
       </c>
       <c r="T5">
-        <v>1.135989244686521</v>
+        <v>1.14782246598534</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>64.33673188791769</v>
+        <v>48.25254891593826</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.102511777568172</v>
+        <v>0.102556777568172</v>
       </c>
       <c r="C6">
-        <v>287.1311053266875</v>
+        <v>284.0488063249047</v>
       </c>
       <c r="D6">
-        <v>223.8795053266875</v>
+        <v>223.7843063249047</v>
       </c>
       <c r="E6">
-        <v>6.038400000000001</v>
+        <v>9.025500000000003</v>
       </c>
       <c r="F6">
-        <v>11.9484</v>
+        <v>14.9355</v>
       </c>
       <c r="G6">
         <v>75.2</v>
@@ -1779,28 +1779,28 @@
         <v>29</v>
       </c>
       <c r="M6">
-        <v>0.60100452</v>
+        <v>0.7512556500000001</v>
       </c>
       <c r="N6">
-        <v>28.39899548</v>
+        <v>28.24874435</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>28.39899548</v>
+        <v>28.24874435</v>
       </c>
       <c r="Q6">
-        <v>33.29899548</v>
+        <v>33.14874435</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1046872683001791</v>
+        <v>0.1053071342822863</v>
       </c>
       <c r="T6">
-        <v>1.14782246598534</v>
+        <v>1.159904807732553</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>48.25254891593826</v>
+        <v>38.60203913275061</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.102556777568172</v>
+        <v>0.102601777568172</v>
       </c>
       <c r="C7">
-        <v>284.0488063249047</v>
+        <v>280.9665882505637</v>
       </c>
       <c r="D7">
-        <v>223.7843063249047</v>
+        <v>223.6891882505637</v>
       </c>
       <c r="E7">
-        <v>9.025500000000003</v>
+        <v>12.0126</v>
       </c>
       <c r="F7">
-        <v>14.9355</v>
+        <v>17.9226</v>
       </c>
       <c r="G7">
         <v>75.2</v>
@@ -1861,28 +1861,28 @@
         <v>29</v>
       </c>
       <c r="M7">
-        <v>0.7512556500000001</v>
+        <v>0.9015067800000001</v>
       </c>
       <c r="N7">
-        <v>28.24874435</v>
+        <v>28.09849322</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>28.24874435</v>
+        <v>28.09849322</v>
       </c>
       <c r="Q7">
-        <v>33.14874435</v>
+        <v>32.99849322</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1053071342822863</v>
+        <v>0.1059401889023106</v>
       </c>
       <c r="T7">
-        <v>1.159904807732553</v>
+        <v>1.172244220580772</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>38.60203913275061</v>
+        <v>32.16836594395885</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.102601777568172</v>
+        <v>0.102646777568172</v>
       </c>
       <c r="C8">
-        <v>280.9665882505638</v>
+        <v>277.8844510005155</v>
       </c>
       <c r="D8">
-        <v>223.6891882505638</v>
+        <v>223.5941510005155</v>
       </c>
       <c r="E8">
-        <v>12.0126</v>
+        <v>14.9997</v>
       </c>
       <c r="F8">
-        <v>17.9226</v>
+        <v>20.9097</v>
       </c>
       <c r="G8">
         <v>75.2</v>
@@ -1943,28 +1943,28 @@
         <v>29</v>
       </c>
       <c r="M8">
-        <v>0.9015067800000001</v>
+        <v>1.05175791</v>
       </c>
       <c r="N8">
-        <v>28.09849322</v>
+        <v>27.94824209</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>28.09849322</v>
+        <v>27.94824209</v>
       </c>
       <c r="Q8">
-        <v>32.99849322</v>
+        <v>32.84824209</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1059401889023106</v>
+        <v>0.1065868576001849</v>
       </c>
       <c r="T8">
-        <v>1.172244220580772</v>
+        <v>1.184848997146157</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>32.16836594395885</v>
+        <v>27.57288509482187</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1026467775681719</v>
+        <v>0.102691777568172</v>
       </c>
       <c r="C9">
-        <v>277.8844510005155</v>
+        <v>274.802394471786</v>
       </c>
       <c r="D9">
-        <v>223.5941510005155</v>
+        <v>223.499194471786</v>
       </c>
       <c r="E9">
-        <v>14.9997</v>
+        <v>17.9868</v>
       </c>
       <c r="F9">
-        <v>20.9097</v>
+        <v>23.8968</v>
       </c>
       <c r="G9">
         <v>75.2</v>
@@ -2025,28 +2025,28 @@
         <v>29</v>
       </c>
       <c r="M9">
-        <v>1.05175791</v>
+        <v>1.20200904</v>
       </c>
       <c r="N9">
-        <v>27.94824209</v>
+        <v>27.79799096</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>27.94824209</v>
+        <v>27.79799096</v>
       </c>
       <c r="Q9">
-        <v>32.84824209</v>
+        <v>32.69799096</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1065868576001849</v>
+        <v>0.1072475843132304</v>
       </c>
       <c r="T9">
-        <v>1.184848997146157</v>
+        <v>1.197727790593398</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>27.57288509482187</v>
+        <v>24.12627445796913</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.102691777568172</v>
+        <v>0.102736777568172</v>
       </c>
       <c r="C10">
-        <v>274.802394471786</v>
+        <v>271.7204185615761</v>
       </c>
       <c r="D10">
-        <v>223.499194471786</v>
+        <v>223.4043185615761</v>
       </c>
       <c r="E10">
-        <v>17.9868</v>
+        <v>20.9739</v>
       </c>
       <c r="F10">
-        <v>23.8968</v>
+        <v>26.8839</v>
       </c>
       <c r="G10">
         <v>75.2</v>
@@ -2107,28 +2107,28 @@
         <v>29</v>
       </c>
       <c r="M10">
-        <v>1.20200904</v>
+        <v>1.35226017</v>
       </c>
       <c r="N10">
-        <v>27.79799096</v>
+        <v>27.64773983</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>27.79799096</v>
+        <v>27.64773983</v>
       </c>
       <c r="Q10">
-        <v>32.69799096</v>
+        <v>32.54773983</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1072475843132304</v>
+        <v>0.1079228324924967</v>
       </c>
       <c r="T10">
-        <v>1.197727790593398</v>
+        <v>1.210889634446072</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>24.12627445796913</v>
+        <v>21.44557729597257</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.102736777568172</v>
+        <v>0.102781777568172</v>
       </c>
       <c r="C11">
-        <v>271.7204185615761</v>
+        <v>268.6385231672612</v>
       </c>
       <c r="D11">
-        <v>223.4043185615761</v>
+        <v>223.3095231672611</v>
       </c>
       <c r="E11">
-        <v>20.9739</v>
+        <v>23.961</v>
       </c>
       <c r="F11">
-        <v>26.8839</v>
+        <v>29.871</v>
       </c>
       <c r="G11">
         <v>75.2</v>
@@ -2189,28 +2189,28 @@
         <v>29</v>
       </c>
       <c r="M11">
-        <v>1.35226017</v>
+        <v>1.5025113</v>
       </c>
       <c r="N11">
-        <v>27.64773983</v>
+        <v>27.4974887</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>27.64773983</v>
+        <v>27.4974887</v>
       </c>
       <c r="Q11">
-        <v>32.54773983</v>
+        <v>32.3974887</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1079228324924967</v>
+        <v>0.1086130861868577</v>
       </c>
       <c r="T11">
-        <v>1.210889634446072</v>
+        <v>1.224343963717695</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>21.44557729597257</v>
+        <v>19.30101956637531</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.102781777568172</v>
+        <v>0.102826777568172</v>
       </c>
       <c r="C12">
-        <v>268.6385231672612</v>
+        <v>265.5567081863906</v>
       </c>
       <c r="D12">
-        <v>223.3095231672611</v>
+        <v>223.2148081863905</v>
       </c>
       <c r="E12">
-        <v>23.96100000000001</v>
+        <v>26.94810000000001</v>
       </c>
       <c r="F12">
-        <v>29.87100000000001</v>
+        <v>32.85810000000001</v>
       </c>
       <c r="G12">
         <v>75.2</v>
@@ -2271,28 +2271,28 @@
         <v>29</v>
       </c>
       <c r="M12">
-        <v>1.5025113</v>
+        <v>1.65276243</v>
       </c>
       <c r="N12">
-        <v>27.4974887</v>
+        <v>27.34723757</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>27.4974887</v>
+        <v>27.34723757</v>
       </c>
       <c r="Q12">
-        <v>32.3974887</v>
+        <v>32.24723757</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1086130861868577</v>
+        <v>0.1093188512001932</v>
       </c>
       <c r="T12">
-        <v>1.224343963717695</v>
+        <v>1.238100637467332</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>19.30101956637531</v>
+        <v>17.54638142397755</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.102826777568172</v>
+        <v>0.102871777568172</v>
       </c>
       <c r="C13">
-        <v>265.5567081863906</v>
+        <v>262.4749735166874</v>
       </c>
       <c r="D13">
-        <v>223.2148081863905</v>
+        <v>223.1201735166875</v>
       </c>
       <c r="E13">
-        <v>26.94810000000001</v>
+        <v>29.93520000000001</v>
       </c>
       <c r="F13">
-        <v>32.85810000000001</v>
+        <v>35.84520000000001</v>
       </c>
       <c r="G13">
         <v>75.2</v>
@@ -2353,28 +2353,28 @@
         <v>29</v>
       </c>
       <c r="M13">
-        <v>1.65276243</v>
+        <v>1.80301356</v>
       </c>
       <c r="N13">
-        <v>27.34723757</v>
+        <v>27.19698644</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>27.34723757</v>
+        <v>27.19698644</v>
       </c>
       <c r="Q13">
-        <v>32.24723757</v>
+        <v>32.09698643999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1093188512001932</v>
+        <v>0.1100406563274682</v>
       </c>
       <c r="T13">
-        <v>1.238100637467332</v>
+        <v>1.252169962893097</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.54638142397755</v>
+        <v>16.08418297197942</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.102871777568172</v>
+        <v>0.102916777568172</v>
       </c>
       <c r="C14">
-        <v>262.4749735166874</v>
+        <v>259.3933190560485</v>
       </c>
       <c r="D14">
-        <v>223.1201735166875</v>
+        <v>223.0256190560486</v>
       </c>
       <c r="E14">
-        <v>29.93520000000001</v>
+        <v>32.92230000000001</v>
       </c>
       <c r="F14">
-        <v>35.84520000000001</v>
+        <v>38.8323</v>
       </c>
       <c r="G14">
         <v>75.2</v>
@@ -2435,28 +2435,28 @@
         <v>29</v>
       </c>
       <c r="M14">
-        <v>1.80301356</v>
+        <v>1.95326469</v>
       </c>
       <c r="N14">
-        <v>27.19698644</v>
+        <v>27.04673531</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>27.19698644</v>
+        <v>27.04673531</v>
       </c>
       <c r="Q14">
-        <v>32.09698643999999</v>
+        <v>31.94673531</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1100406563274682</v>
+        <v>0.1107790546760597</v>
       </c>
       <c r="T14">
-        <v>1.252169962893097</v>
+        <v>1.266562721087271</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.08418297197942</v>
+        <v>14.84693812798101</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.102916777568172</v>
+        <v>0.102961777568172</v>
       </c>
       <c r="C15">
-        <v>259.3933190560485</v>
+        <v>256.3117447025432</v>
       </c>
       <c r="D15">
-        <v>223.0256190560486</v>
+        <v>222.9311447025432</v>
       </c>
       <c r="E15">
-        <v>32.92230000000001</v>
+        <v>35.90940000000001</v>
       </c>
       <c r="F15">
-        <v>38.8323</v>
+        <v>41.81940000000001</v>
       </c>
       <c r="G15">
         <v>75.2</v>
@@ -2517,28 +2517,28 @@
         <v>29</v>
       </c>
       <c r="M15">
-        <v>1.95326469</v>
+        <v>2.10351582</v>
       </c>
       <c r="N15">
-        <v>27.04673531</v>
+        <v>26.89648418</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>27.04673531</v>
+        <v>26.89648418</v>
       </c>
       <c r="Q15">
-        <v>31.94673531</v>
+        <v>31.79648418</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1107790546760597</v>
+        <v>0.1115346250792698</v>
       </c>
       <c r="T15">
-        <v>1.266562721087271</v>
+        <v>1.281290194588286</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.84693812798101</v>
+        <v>13.78644254741093</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.102961777568172</v>
+        <v>0.103231777568172</v>
       </c>
       <c r="C16">
-        <v>256.3117447025432</v>
+        <v>252.7594751449212</v>
       </c>
       <c r="D16">
-        <v>222.9311447025432</v>
+        <v>222.3659751449212</v>
       </c>
       <c r="E16">
-        <v>35.90940000000001</v>
+        <v>38.89650000000002</v>
       </c>
       <c r="F16">
-        <v>41.81940000000001</v>
+        <v>44.80650000000001</v>
       </c>
       <c r="G16">
         <v>75.2</v>
@@ -2599,45 +2599,45 @@
         <v>29</v>
       </c>
       <c r="M16">
-        <v>2.10351582</v>
+        <v>2.320976700000001</v>
       </c>
       <c r="N16">
-        <v>26.89648418</v>
+        <v>26.6790233</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>26.89648418</v>
+        <v>26.6790233</v>
       </c>
       <c r="Q16">
-        <v>31.79648418</v>
+        <v>31.5790233</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1115346250792698</v>
+        <v>0.1123079736096141</v>
       </c>
       <c r="T16">
-        <v>1.281290194588286</v>
+        <v>1.29636419687756</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0</v>
       </c>
       <c r="W16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.78644254741093</v>
+        <v>12.49473982224811</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.103231777568172</v>
+        <v>0.103291777568172</v>
       </c>
       <c r="C17">
-        <v>252.7594751449213</v>
+        <v>249.6471708474109</v>
       </c>
       <c r="D17">
-        <v>222.3659751449212</v>
+        <v>222.2407708474109</v>
       </c>
       <c r="E17">
-        <v>38.8965</v>
+        <v>41.8836</v>
       </c>
       <c r="F17">
-        <v>44.80650000000001</v>
+        <v>47.7936</v>
       </c>
       <c r="G17">
         <v>75.2</v>
@@ -2681,28 +2681,28 @@
         <v>29</v>
       </c>
       <c r="M17">
-        <v>2.3209767</v>
+        <v>2.47570848</v>
       </c>
       <c r="N17">
-        <v>26.6790233</v>
+        <v>26.52429152</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>26.6790233</v>
+        <v>26.52429152</v>
       </c>
       <c r="Q17">
-        <v>31.5790233</v>
+        <v>31.42429152</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1123079736096141</v>
+        <v>0.1130997352002047</v>
       </c>
       <c r="T17">
-        <v>1.29636419687756</v>
+        <v>1.311797103983245</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.49473982224811</v>
+        <v>11.7138185833576</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.103291777568172</v>
+        <v>0.103351777568172</v>
       </c>
       <c r="C18">
-        <v>249.6471708474109</v>
+        <v>246.5350074643958</v>
       </c>
       <c r="D18">
-        <v>222.2407708474109</v>
+        <v>222.1157074643958</v>
       </c>
       <c r="E18">
-        <v>41.8836</v>
+        <v>44.87070000000001</v>
       </c>
       <c r="F18">
-        <v>47.7936</v>
+        <v>50.78070000000001</v>
       </c>
       <c r="G18">
         <v>75.2</v>
@@ -2763,28 +2763,28 @@
         <v>29</v>
       </c>
       <c r="M18">
-        <v>2.47570848</v>
+        <v>2.63044026</v>
       </c>
       <c r="N18">
-        <v>26.52429152</v>
+        <v>26.36955974</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>26.52429152</v>
+        <v>26.36955974</v>
       </c>
       <c r="Q18">
-        <v>31.42429152</v>
+        <v>31.26955974</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1130997352002047</v>
+        <v>0.1139105753833397</v>
       </c>
       <c r="T18">
-        <v>1.311797103983245</v>
+        <v>1.327601888368585</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.7138185833576</v>
+        <v>11.02477043139539</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.103351777568172</v>
+        <v>0.103411777568172</v>
       </c>
       <c r="C19">
-        <v>246.5350074643958</v>
+        <v>243.4229847581157</v>
       </c>
       <c r="D19">
-        <v>222.1157074643958</v>
+        <v>221.9907847581157</v>
       </c>
       <c r="E19">
-        <v>44.87070000000001</v>
+        <v>47.85780000000001</v>
       </c>
       <c r="F19">
-        <v>50.78070000000001</v>
+        <v>53.76780000000002</v>
       </c>
       <c r="G19">
         <v>75.2</v>
@@ -2845,28 +2845,28 @@
         <v>29</v>
       </c>
       <c r="M19">
-        <v>2.63044026</v>
+        <v>2.785172040000001</v>
       </c>
       <c r="N19">
-        <v>26.36955974</v>
+        <v>26.21482796</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>26.36955974</v>
+        <v>26.21482796</v>
       </c>
       <c r="Q19">
-        <v>31.26955974</v>
+        <v>31.11482796</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1139105753833397</v>
+        <v>0.1147411921563073</v>
       </c>
       <c r="T19">
-        <v>1.327601888368585</v>
+        <v>1.343792155299909</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.02477043139539</v>
+        <v>10.41228318520675</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.103411777568172</v>
+        <v>0.103471777568172</v>
       </c>
       <c r="C20">
-        <v>243.4229847581156</v>
+        <v>240.3111024913451</v>
       </c>
       <c r="D20">
-        <v>221.9907847581156</v>
+        <v>221.8660024913451</v>
       </c>
       <c r="E20">
-        <v>47.8578</v>
+        <v>50.84490000000001</v>
       </c>
       <c r="F20">
-        <v>53.7678</v>
+        <v>56.75490000000001</v>
       </c>
       <c r="G20">
         <v>75.2</v>
@@ -2927,28 +2927,28 @@
         <v>29</v>
       </c>
       <c r="M20">
-        <v>2.78517204</v>
+        <v>2.93990382</v>
       </c>
       <c r="N20">
-        <v>26.21482796</v>
+        <v>26.06009618</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>26.21482796</v>
+        <v>26.06009618</v>
       </c>
       <c r="Q20">
-        <v>31.11482796</v>
+        <v>30.96009618</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1147411921563073</v>
+        <v>0.1155923179853975</v>
       </c>
       <c r="T20">
-        <v>1.343792155299909</v>
+        <v>1.36038218190855</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.41228318520676</v>
+        <v>9.86426828072219</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.103471777568172</v>
+        <v>0.103871777568172</v>
       </c>
       <c r="C21">
-        <v>240.3111024913451</v>
+        <v>236.4956923036812</v>
       </c>
       <c r="D21">
-        <v>221.8660024913451</v>
+        <v>221.0376923036812</v>
       </c>
       <c r="E21">
-        <v>50.84490000000001</v>
+        <v>53.83200000000001</v>
       </c>
       <c r="F21">
-        <v>56.75490000000001</v>
+        <v>59.74200000000001</v>
       </c>
       <c r="G21">
         <v>75.2</v>
@@ -3009,45 +3009,45 @@
         <v>29</v>
       </c>
       <c r="M21">
-        <v>2.93990382</v>
+        <v>3.196197000000001</v>
       </c>
       <c r="N21">
-        <v>26.06009618</v>
+        <v>25.803803</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>26.06009618</v>
+        <v>25.803803</v>
       </c>
       <c r="Q21">
-        <v>30.96009618</v>
+        <v>30.703803</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1155923179853975</v>
+        <v>0.116464721960215</v>
       </c>
       <c r="T21">
-        <v>1.36038218190855</v>
+        <v>1.377386959182407</v>
       </c>
       <c r="U21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V21">
         <v>0</v>
       </c>
       <c r="W21">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y21">
-        <v>9.86426828072219</v>
+        <v>9.073283029800727</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.103871777568172</v>
+        <v>0.103948777568172</v>
       </c>
       <c r="C22">
-        <v>236.4956923036812</v>
+        <v>233.3498519618149</v>
       </c>
       <c r="D22">
-        <v>221.0376923036812</v>
+        <v>220.8789519618149</v>
       </c>
       <c r="E22">
-        <v>53.83200000000001</v>
+        <v>56.81910000000002</v>
       </c>
       <c r="F22">
-        <v>59.74200000000001</v>
+        <v>62.72910000000002</v>
       </c>
       <c r="G22">
         <v>75.2</v>
@@ -3091,28 +3091,28 @@
         <v>29</v>
       </c>
       <c r="M22">
-        <v>3.196197000000001</v>
+        <v>3.356006850000001</v>
       </c>
       <c r="N22">
-        <v>25.803803</v>
+        <v>25.64399315</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>25.803803</v>
+        <v>25.64399315</v>
       </c>
       <c r="Q22">
-        <v>30.703803</v>
+        <v>30.54399315</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.116464721960215</v>
+        <v>0.1173592121116101</v>
       </c>
       <c r="T22">
-        <v>1.377386959182407</v>
+        <v>1.394822237146742</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>9.073283029800727</v>
+        <v>8.641221933143548</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.103948777568172</v>
+        <v>0.104025777568172</v>
       </c>
       <c r="C23">
-        <v>233.3498519618149</v>
+        <v>230.204239458127</v>
       </c>
       <c r="D23">
-        <v>220.8789519618149</v>
+        <v>220.720439458127</v>
       </c>
       <c r="E23">
-        <v>56.81910000000001</v>
+        <v>59.80620000000002</v>
       </c>
       <c r="F23">
-        <v>62.7291</v>
+        <v>65.71620000000001</v>
       </c>
       <c r="G23">
         <v>75.2</v>
@@ -3173,28 +3173,28 @@
         <v>29</v>
       </c>
       <c r="M23">
-        <v>3.35600685</v>
+        <v>3.515816700000001</v>
       </c>
       <c r="N23">
-        <v>25.64399315</v>
+        <v>25.4841833</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>25.64399315</v>
+        <v>25.4841833</v>
       </c>
       <c r="Q23">
-        <v>30.54399315</v>
+        <v>30.3841833</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1173592121116101</v>
+        <v>0.1182766379079128</v>
       </c>
       <c r="T23">
-        <v>1.394822237146742</v>
+        <v>1.412704573520418</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.641221933143552</v>
+        <v>8.248439118000661</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.104025777568172</v>
+        <v>0.104102777568172</v>
       </c>
       <c r="C24">
-        <v>230.204239458127</v>
+        <v>227.058854302449</v>
       </c>
       <c r="D24">
-        <v>220.720439458127</v>
+        <v>220.562154302449</v>
       </c>
       <c r="E24">
-        <v>59.80620000000002</v>
+        <v>62.79330000000002</v>
       </c>
       <c r="F24">
-        <v>65.71620000000001</v>
+        <v>68.70330000000001</v>
       </c>
       <c r="G24">
         <v>75.2</v>
@@ -3255,28 +3255,28 @@
         <v>29</v>
       </c>
       <c r="M24">
-        <v>3.515816700000001</v>
+        <v>3.67562655</v>
       </c>
       <c r="N24">
-        <v>25.4841833</v>
+        <v>25.32437345</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>25.4841833</v>
+        <v>25.32437345</v>
       </c>
       <c r="Q24">
-        <v>30.3841833</v>
+        <v>30.22437345</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1182766379079128</v>
+        <v>0.1192178929456779</v>
       </c>
       <c r="T24">
-        <v>1.412704573520418</v>
+        <v>1.43105138616354</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.248439118000661</v>
+        <v>7.889811330261502</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.104102777568172</v>
+        <v>0.104371777568172</v>
       </c>
       <c r="C25">
-        <v>227.058854302449</v>
+        <v>223.5205615360573</v>
       </c>
       <c r="D25">
-        <v>220.562154302449</v>
+        <v>220.0109615360573</v>
       </c>
       <c r="E25">
-        <v>62.79330000000002</v>
+        <v>65.78040000000001</v>
       </c>
       <c r="F25">
-        <v>68.70330000000001</v>
+        <v>71.69040000000001</v>
       </c>
       <c r="G25">
         <v>75.2</v>
@@ -3337,45 +3337,45 @@
         <v>29</v>
       </c>
       <c r="M25">
-        <v>3.67562655</v>
+        <v>3.892788720000001</v>
       </c>
       <c r="N25">
-        <v>25.32437345</v>
+        <v>25.10721128</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>25.32437345</v>
+        <v>25.10721128</v>
       </c>
       <c r="Q25">
-        <v>30.22437345</v>
+        <v>30.00721128</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1192178929456779</v>
+        <v>0.1201839178528579</v>
       </c>
       <c r="T25">
-        <v>1.43105138616354</v>
+        <v>1.449881009665692</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.889811330261502</v>
+        <v>7.449672223670025</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.104371777568172</v>
+        <v>0.104456777568172</v>
       </c>
       <c r="C26">
-        <v>223.5205615360573</v>
+        <v>220.3598651537611</v>
       </c>
       <c r="D26">
-        <v>220.0109615360573</v>
+        <v>219.8373651537611</v>
       </c>
       <c r="E26">
-        <v>65.78040000000001</v>
+        <v>68.76750000000001</v>
       </c>
       <c r="F26">
-        <v>71.69040000000001</v>
+        <v>74.67750000000001</v>
       </c>
       <c r="G26">
         <v>75.2</v>
@@ -3419,28 +3419,28 @@
         <v>29</v>
       </c>
       <c r="M26">
-        <v>3.892788720000001</v>
+        <v>4.054988250000001</v>
       </c>
       <c r="N26">
-        <v>25.10721128</v>
+        <v>24.94501175</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>25.10721128</v>
+        <v>24.94501175</v>
       </c>
       <c r="Q26">
-        <v>30.00721128</v>
+        <v>29.84501175</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1201839178528579</v>
+        <v>0.1211757034242293</v>
       </c>
       <c r="T26">
-        <v>1.449881009665692</v>
+        <v>1.469212756461234</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.449672223670025</v>
+        <v>7.151685334723225</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.104456777568172</v>
+        <v>0.104541777568172</v>
       </c>
       <c r="C27">
-        <v>220.3598651537611</v>
+        <v>217.1994425027766</v>
       </c>
       <c r="D27">
-        <v>219.8373651537611</v>
+        <v>219.6640425027766</v>
       </c>
       <c r="E27">
-        <v>68.76750000000001</v>
+        <v>71.75460000000001</v>
       </c>
       <c r="F27">
-        <v>74.67750000000001</v>
+        <v>77.66460000000001</v>
       </c>
       <c r="G27">
         <v>75.2</v>
@@ -3501,28 +3501,28 @@
         <v>29</v>
       </c>
       <c r="M27">
-        <v>4.054988250000001</v>
+        <v>4.217187780000001</v>
       </c>
       <c r="N27">
-        <v>24.94501175</v>
+        <v>24.78281222</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>24.94501175</v>
+        <v>24.78281222</v>
       </c>
       <c r="Q27">
-        <v>29.84501175</v>
+        <v>29.68281222</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1211757034242293</v>
+        <v>0.1221942940110432</v>
       </c>
       <c r="T27">
-        <v>1.469212756461234</v>
+        <v>1.4890669828999</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.151685334723225</v>
+        <v>6.876620514156948</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.104541777568172</v>
+        <v>0.104626777568172</v>
       </c>
       <c r="C28">
-        <v>217.1994425027766</v>
+        <v>214.039292936174</v>
       </c>
       <c r="D28">
-        <v>219.6640425027766</v>
+        <v>219.490992936174</v>
       </c>
       <c r="E28">
-        <v>71.75460000000001</v>
+        <v>74.74170000000002</v>
       </c>
       <c r="F28">
-        <v>77.66460000000001</v>
+        <v>80.65170000000002</v>
       </c>
       <c r="G28">
         <v>75.2</v>
@@ -3583,28 +3583,28 @@
         <v>29</v>
       </c>
       <c r="M28">
-        <v>4.217187780000001</v>
+        <v>4.379387310000001</v>
       </c>
       <c r="N28">
-        <v>24.78281222</v>
+        <v>24.62061269</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>24.78281222</v>
+        <v>24.62061269</v>
       </c>
       <c r="Q28">
-        <v>29.68281222</v>
+        <v>29.52061269</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1221942940110432</v>
+        <v>0.1232407911892767</v>
       </c>
       <c r="T28">
-        <v>1.4890669828999</v>
+        <v>1.509465160747844</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.876620514156948</v>
+        <v>6.621930865484467</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.104626777568172</v>
+        <v>0.104711777568172</v>
       </c>
       <c r="C29">
-        <v>214.039292936174</v>
+        <v>210.8794158090604</v>
       </c>
       <c r="D29">
-        <v>219.490992936174</v>
+        <v>219.3182158090604</v>
       </c>
       <c r="E29">
-        <v>74.74170000000002</v>
+        <v>77.72880000000002</v>
       </c>
       <c r="F29">
-        <v>80.65170000000002</v>
+        <v>83.63880000000002</v>
       </c>
       <c r="G29">
         <v>75.2</v>
@@ -3665,28 +3665,28 @@
         <v>29</v>
       </c>
       <c r="M29">
-        <v>4.379387310000001</v>
+        <v>4.541586840000001</v>
       </c>
       <c r="N29">
-        <v>24.62061269</v>
+        <v>24.45841316</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>24.62061269</v>
+        <v>24.45841316</v>
       </c>
       <c r="Q29">
-        <v>29.52061269</v>
+        <v>29.35841316</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1232407911892767</v>
+        <v>0.1243163577335722</v>
       </c>
       <c r="T29">
-        <v>1.509465160747844</v>
+        <v>1.530429954647119</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.621930865484467</v>
+        <v>6.385433334574308</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.104711777568172</v>
+        <v>0.104796777568172</v>
       </c>
       <c r="C30">
-        <v>210.8794158090604</v>
+        <v>207.7198104785716</v>
       </c>
       <c r="D30">
-        <v>219.3182158090604</v>
+        <v>219.1457104785716</v>
       </c>
       <c r="E30">
-        <v>77.72880000000002</v>
+        <v>80.71590000000002</v>
       </c>
       <c r="F30">
-        <v>83.63880000000002</v>
+        <v>86.62590000000002</v>
       </c>
       <c r="G30">
         <v>75.2</v>
@@ -3747,28 +3747,28 @@
         <v>29</v>
       </c>
       <c r="M30">
-        <v>4.541586840000001</v>
+        <v>4.703786370000001</v>
       </c>
       <c r="N30">
-        <v>24.45841316</v>
+        <v>24.29621363</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>24.45841316</v>
+        <v>24.29621363</v>
       </c>
       <c r="Q30">
-        <v>29.35841316</v>
+        <v>29.19621363</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1243163577335722</v>
+        <v>0.1254222219270028</v>
       </c>
       <c r="T30">
-        <v>1.530429954647119</v>
+        <v>1.551985306121022</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.385433334574308</v>
+        <v>6.165245978209676</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.104796777568172</v>
+        <v>0.105181777568172</v>
       </c>
       <c r="C31">
-        <v>207.7198104785716</v>
+        <v>203.9547489583091</v>
       </c>
       <c r="D31">
-        <v>219.1457104785716</v>
+        <v>218.3677489583091</v>
       </c>
       <c r="E31">
-        <v>80.7159</v>
+        <v>83.70300000000002</v>
       </c>
       <c r="F31">
-        <v>86.6259</v>
+        <v>89.61300000000001</v>
       </c>
       <c r="G31">
         <v>75.2</v>
@@ -3829,45 +3829,45 @@
         <v>29</v>
       </c>
       <c r="M31">
-        <v>4.70378637</v>
+        <v>4.955598900000001</v>
       </c>
       <c r="N31">
-        <v>24.29621363</v>
+        <v>24.0444011</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>24.29621363</v>
+        <v>24.0444011</v>
       </c>
       <c r="Q31">
-        <v>29.19621363</v>
+        <v>28.9444011</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1254222219270028</v>
+        <v>0.1265596822402457</v>
       </c>
       <c r="T31">
-        <v>1.551985306121022</v>
+        <v>1.574156524779894</v>
       </c>
       <c r="U31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V31">
         <v>0</v>
       </c>
       <c r="W31">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y31">
-        <v>6.165245978209677</v>
+        <v>5.85196675219215</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.105181777568172</v>
+        <v>0.105276777568172</v>
       </c>
       <c r="C32">
-        <v>203.9547489583091</v>
+        <v>200.77653330749</v>
       </c>
       <c r="D32">
-        <v>218.3677489583091</v>
+        <v>218.17663330749</v>
       </c>
       <c r="E32">
-        <v>83.70300000000002</v>
+        <v>86.69010000000002</v>
       </c>
       <c r="F32">
-        <v>89.61300000000001</v>
+        <v>92.60010000000001</v>
       </c>
       <c r="G32">
         <v>75.2</v>
@@ -3911,28 +3911,28 @@
         <v>29</v>
       </c>
       <c r="M32">
-        <v>4.955598900000001</v>
+        <v>5.120785530000001</v>
       </c>
       <c r="N32">
-        <v>24.0444011</v>
+        <v>23.87921447</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>24.0444011</v>
+        <v>23.87921447</v>
       </c>
       <c r="Q32">
-        <v>28.9444011</v>
+        <v>28.77921447</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1265596822402457</v>
+        <v>0.1277301124176405</v>
       </c>
       <c r="T32">
-        <v>1.574156524779894</v>
+        <v>1.596970387457864</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.85196675219215</v>
+        <v>5.663193631153694</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.105276777568172</v>
+        <v>0.105371777568172</v>
       </c>
       <c r="C33">
-        <v>200.77653330749</v>
+        <v>197.5986518933266</v>
       </c>
       <c r="D33">
-        <v>218.17663330749</v>
+        <v>217.9858518933266</v>
       </c>
       <c r="E33">
-        <v>86.69010000000002</v>
+        <v>89.67720000000001</v>
       </c>
       <c r="F33">
-        <v>92.60010000000001</v>
+        <v>95.58720000000001</v>
       </c>
       <c r="G33">
         <v>75.2</v>
@@ -3993,28 +3993,28 @@
         <v>29</v>
       </c>
       <c r="M33">
-        <v>5.120785530000001</v>
+        <v>5.285972160000001</v>
       </c>
       <c r="N33">
-        <v>23.87921447</v>
+        <v>23.71402784</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>23.87921447</v>
+        <v>23.71402784</v>
       </c>
       <c r="Q33">
-        <v>28.77921447</v>
+        <v>28.61402784</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1277301124176405</v>
+        <v>0.1289349670120176</v>
       </c>
       <c r="T33">
-        <v>1.596970387457864</v>
+        <v>1.62045524609695</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.663193631153694</v>
+        <v>5.486218830180142</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.105371777568172</v>
+        <v>0.105466777568172</v>
       </c>
       <c r="C34">
-        <v>197.5986518933266</v>
+        <v>194.4211038397795</v>
       </c>
       <c r="D34">
-        <v>217.9858518933266</v>
+        <v>217.7954038397796</v>
       </c>
       <c r="E34">
-        <v>89.67720000000001</v>
+        <v>92.66430000000003</v>
       </c>
       <c r="F34">
-        <v>95.58720000000001</v>
+        <v>98.57430000000002</v>
       </c>
       <c r="G34">
         <v>75.2</v>
@@ -4075,28 +4075,28 @@
         <v>29</v>
       </c>
       <c r="M34">
-        <v>5.285972160000001</v>
+        <v>5.451158790000002</v>
       </c>
       <c r="N34">
-        <v>23.71402784</v>
+        <v>23.54884121</v>
       </c>
       <c r="O34">
         <v>0</v>
       </c>
       <c r="P34">
-        <v>23.71402784</v>
+        <v>23.54884121</v>
       </c>
       <c r="Q34">
-        <v>28.61402784</v>
+        <v>28.44884121</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1289349670120176</v>
+        <v>0.1301757874151821</v>
       </c>
       <c r="T34">
-        <v>1.62045524609695</v>
+        <v>1.644641145292427</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.486218830180142</v>
+        <v>5.319969774720136</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.105466777568172</v>
+        <v>0.105561777568172</v>
       </c>
       <c r="C35">
-        <v>194.4211038397795</v>
+        <v>191.2438882738686</v>
       </c>
       <c r="D35">
-        <v>217.7954038397796</v>
+        <v>217.6052882738686</v>
       </c>
       <c r="E35">
-        <v>92.66430000000003</v>
+        <v>95.65140000000002</v>
       </c>
       <c r="F35">
-        <v>98.57430000000002</v>
+        <v>101.5614</v>
       </c>
       <c r="G35">
         <v>75.2</v>
@@ -4157,28 +4157,28 @@
         <v>29</v>
       </c>
       <c r="M35">
-        <v>5.451158790000002</v>
+        <v>5.616345420000001</v>
       </c>
       <c r="N35">
-        <v>23.54884121</v>
+        <v>23.38365458</v>
       </c>
       <c r="O35">
         <v>0</v>
       </c>
       <c r="P35">
-        <v>23.54884121</v>
+        <v>23.38365458</v>
       </c>
       <c r="Q35">
-        <v>28.44884121</v>
+        <v>28.28365458</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1301757874151821</v>
+        <v>0.1314542084366242</v>
       </c>
       <c r="T35">
-        <v>1.644641145292427</v>
+        <v>1.66955995052413</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.319969774720136</v>
+        <v>5.163500075463662</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.105561777568172</v>
+        <v>0.105656777568172</v>
       </c>
       <c r="C36">
-        <v>191.2438882738686</v>
+        <v>188.0670043256586</v>
       </c>
       <c r="D36">
-        <v>217.6052882738686</v>
+        <v>217.4155043256586</v>
       </c>
       <c r="E36">
-        <v>95.65140000000002</v>
+        <v>98.63850000000002</v>
       </c>
       <c r="F36">
-        <v>101.5614</v>
+        <v>104.5485</v>
       </c>
       <c r="G36">
         <v>75.2</v>
@@ -4239,28 +4239,28 @@
         <v>29</v>
       </c>
       <c r="M36">
-        <v>5.616345420000001</v>
+        <v>5.781532050000001</v>
       </c>
       <c r="N36">
-        <v>23.38365458</v>
+        <v>23.21846795</v>
       </c>
       <c r="O36">
         <v>0</v>
       </c>
       <c r="P36">
-        <v>23.38365458</v>
+        <v>23.21846795</v>
       </c>
       <c r="Q36">
-        <v>28.28365458</v>
+        <v>28.11846795</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1314542084366242</v>
+        <v>0.1327719654894954</v>
       </c>
       <c r="T36">
-        <v>1.66955995052413</v>
+        <v>1.695245488224501</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.163500075463662</v>
+        <v>5.015971501878986</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.105656777568172</v>
+        <v>0.105751777568172</v>
       </c>
       <c r="C37">
-        <v>188.0670043256586</v>
+        <v>184.8904511282469</v>
       </c>
       <c r="D37">
-        <v>217.4155043256586</v>
+        <v>217.2260511282469</v>
       </c>
       <c r="E37">
-        <v>98.63850000000002</v>
+        <v>101.6256</v>
       </c>
       <c r="F37">
-        <v>104.5485</v>
+        <v>107.5356</v>
       </c>
       <c r="G37">
         <v>75.2</v>
@@ -4321,28 +4321,28 @@
         <v>29</v>
       </c>
       <c r="M37">
-        <v>5.781532050000001</v>
+        <v>5.946718680000002</v>
       </c>
       <c r="N37">
-        <v>23.21846795</v>
+        <v>23.05328132</v>
       </c>
       <c r="O37">
         <v>0</v>
       </c>
       <c r="P37">
-        <v>23.21846795</v>
+        <v>23.05328132</v>
       </c>
       <c r="Q37">
-        <v>28.11846795</v>
+        <v>27.95328131999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1327719654894954</v>
+        <v>0.1341309024502687</v>
       </c>
       <c r="T37">
-        <v>1.695245488224501</v>
+        <v>1.721733698978009</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.015971501878986</v>
+        <v>4.876638960160125</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.105751777568172</v>
+        <v>0.105846777568172</v>
       </c>
       <c r="C38">
-        <v>184.8904511282469</v>
+        <v>181.7142278177497</v>
       </c>
       <c r="D38">
-        <v>217.2260511282469</v>
+        <v>217.0369278177497</v>
       </c>
       <c r="E38">
-        <v>101.6256</v>
+        <v>104.6127</v>
       </c>
       <c r="F38">
-        <v>107.5356</v>
+        <v>110.5227</v>
       </c>
       <c r="G38">
         <v>75.2</v>
@@ -4403,28 +4403,28 @@
         <v>29</v>
       </c>
       <c r="M38">
-        <v>5.94671868</v>
+        <v>6.111905310000001</v>
       </c>
       <c r="N38">
-        <v>23.05328132</v>
+        <v>22.88809469</v>
       </c>
       <c r="O38">
         <v>0</v>
       </c>
       <c r="P38">
-        <v>23.05328132</v>
+        <v>22.88809469</v>
       </c>
       <c r="Q38">
-        <v>27.95328132</v>
+        <v>27.78809469</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1341309024502687</v>
+        <v>0.1355329802669397</v>
       </c>
       <c r="T38">
-        <v>1.721733698978009</v>
+        <v>1.749062805310994</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.876638960160126</v>
+        <v>4.744837907182825</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.105846777568172</v>
+        <v>0.105941777568172</v>
       </c>
       <c r="C39">
-        <v>181.7142278177497</v>
+        <v>178.5383335332891</v>
       </c>
       <c r="D39">
-        <v>217.0369278177497</v>
+        <v>216.8481335332891</v>
       </c>
       <c r="E39">
-        <v>104.6127</v>
+        <v>107.5998</v>
       </c>
       <c r="F39">
-        <v>110.5227</v>
+        <v>113.5098</v>
       </c>
       <c r="G39">
         <v>75.2</v>
@@ -4485,28 +4485,28 @@
         <v>29</v>
       </c>
       <c r="M39">
-        <v>6.111905310000001</v>
+        <v>6.277091940000001</v>
       </c>
       <c r="N39">
-        <v>22.88809469</v>
+        <v>22.72290806</v>
       </c>
       <c r="O39">
         <v>0</v>
       </c>
       <c r="P39">
-        <v>22.88809469</v>
+        <v>22.72290806</v>
       </c>
       <c r="Q39">
-        <v>27.78809469</v>
+        <v>27.62290806</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1355329802669397</v>
+        <v>0.1369802864002774</v>
       </c>
       <c r="T39">
-        <v>1.749062805310994</v>
+        <v>1.777273495719235</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.744837907182825</v>
+        <v>4.619973751730646</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.105941777568172</v>
+        <v>0.106036777568172</v>
       </c>
       <c r="C40">
-        <v>178.5383335332891</v>
+        <v>175.36276741698</v>
       </c>
       <c r="D40">
-        <v>216.8481335332891</v>
+        <v>216.6596674169801</v>
       </c>
       <c r="E40">
-        <v>107.5998</v>
+        <v>110.5869</v>
       </c>
       <c r="F40">
-        <v>113.5098</v>
+        <v>116.4969</v>
       </c>
       <c r="G40">
         <v>75.2</v>
@@ -4567,28 +4567,28 @@
         <v>29</v>
       </c>
       <c r="M40">
-        <v>6.277091940000001</v>
+        <v>6.442278570000002</v>
       </c>
       <c r="N40">
-        <v>22.72290806</v>
+        <v>22.55772143</v>
       </c>
       <c r="O40">
         <v>0</v>
       </c>
       <c r="P40">
-        <v>22.72290806</v>
+        <v>22.55772143</v>
       </c>
       <c r="Q40">
-        <v>27.62290806</v>
+        <v>27.45772143</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1369802864002774</v>
+        <v>0.1384750451937246</v>
       </c>
       <c r="T40">
-        <v>1.777273495719235</v>
+        <v>1.8064091267966</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.619973751730646</v>
+        <v>4.501512886301654</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.106036777568172</v>
+        <v>0.107131777568172</v>
       </c>
       <c r="C41">
-        <v>175.36276741698</v>
+        <v>170.2267625308575</v>
       </c>
       <c r="D41">
-        <v>216.6596674169801</v>
+        <v>214.5107625308575</v>
       </c>
       <c r="E41">
-        <v>110.5869</v>
+        <v>113.574</v>
       </c>
       <c r="F41">
-        <v>116.4969</v>
+        <v>119.484</v>
       </c>
       <c r="G41">
         <v>75.2</v>
@@ -4649,45 +4649,45 @@
         <v>29</v>
       </c>
       <c r="M41">
-        <v>6.442278570000002</v>
+        <v>6.906175200000002</v>
       </c>
       <c r="N41">
-        <v>22.55772143</v>
+        <v>22.0938248</v>
       </c>
       <c r="O41">
         <v>0</v>
       </c>
       <c r="P41">
-        <v>22.55772143</v>
+        <v>22.0938248</v>
       </c>
       <c r="Q41">
-        <v>27.45772143</v>
+        <v>26.9938248</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1384750451937246</v>
+        <v>0.1400196292802866</v>
       </c>
       <c r="T41">
-        <v>1.8064091267966</v>
+        <v>1.836515945576543</v>
       </c>
       <c r="U41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V41">
         <v>0</v>
       </c>
       <c r="W41">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y41">
-        <v>4.501512886301654</v>
+        <v>4.199140502546184</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.107131777568172</v>
+        <v>0.107251777568172</v>
       </c>
       <c r="C42">
-        <v>170.2267625308575</v>
+        <v>167.0067549962079</v>
       </c>
       <c r="D42">
-        <v>214.5107625308575</v>
+        <v>214.277854996208</v>
       </c>
       <c r="E42">
-        <v>113.574</v>
+        <v>116.5611</v>
       </c>
       <c r="F42">
-        <v>119.484</v>
+        <v>122.4711</v>
       </c>
       <c r="G42">
         <v>75.2</v>
@@ -4731,28 +4731,28 @@
         <v>29</v>
       </c>
       <c r="M42">
-        <v>6.906175200000002</v>
+        <v>7.078829580000002</v>
       </c>
       <c r="N42">
-        <v>22.0938248</v>
+        <v>21.92117042</v>
       </c>
       <c r="O42">
         <v>0</v>
       </c>
       <c r="P42">
-        <v>22.0938248</v>
+        <v>21.92117042</v>
       </c>
       <c r="Q42">
-        <v>26.9938248</v>
+        <v>26.82117042</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1400196292802866</v>
+        <v>0.141616572149444</v>
       </c>
       <c r="T42">
-        <v>1.836515945576543</v>
+        <v>1.86764333448462</v>
       </c>
       <c r="U42">
         <v>0.0578</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.199140502546184</v>
+        <v>4.096722441508472</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.107251777568172</v>
+        <v>0.108841777568172</v>
       </c>
       <c r="C43">
-        <v>167.0067549962079</v>
+        <v>160.980700285869</v>
       </c>
       <c r="D43">
-        <v>214.277854996208</v>
+        <v>211.2389002858691</v>
       </c>
       <c r="E43">
-        <v>116.5611</v>
+        <v>119.5482</v>
       </c>
       <c r="F43">
-        <v>122.4711</v>
+        <v>125.4582</v>
       </c>
       <c r="G43">
         <v>75.2</v>
@@ -4813,45 +4813,45 @@
         <v>29</v>
       </c>
       <c r="M43">
-        <v>7.078829580000002</v>
+        <v>7.690587660000002</v>
       </c>
       <c r="N43">
-        <v>21.92117042</v>
+        <v>21.30941234</v>
       </c>
       <c r="O43">
         <v>0</v>
       </c>
       <c r="P43">
-        <v>21.92117042</v>
+        <v>21.30941234</v>
       </c>
       <c r="Q43">
-        <v>26.82117042</v>
+        <v>26.20941234</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.141616572149444</v>
+        <v>0.1432685820140896</v>
       </c>
       <c r="T43">
-        <v>1.86764333448462</v>
+        <v>1.899844081630907</v>
       </c>
       <c r="U43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V43">
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.096722441508472</v>
+        <v>3.770843176371777</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.108841777568172</v>
+        <v>0.108996777568172</v>
       </c>
       <c r="C44">
-        <v>160.9807002858691</v>
+        <v>157.7019547123896</v>
       </c>
       <c r="D44">
-        <v>211.2389002858691</v>
+        <v>210.9472547123895</v>
       </c>
       <c r="E44">
-        <v>119.5482</v>
+        <v>122.5353</v>
       </c>
       <c r="F44">
-        <v>125.4582</v>
+        <v>128.4453</v>
       </c>
       <c r="G44">
         <v>75.2</v>
@@ -4895,28 +4895,28 @@
         <v>29</v>
       </c>
       <c r="M44">
-        <v>7.69058766</v>
+        <v>7.873696890000001</v>
       </c>
       <c r="N44">
-        <v>21.30941234</v>
+        <v>21.12630311</v>
       </c>
       <c r="O44">
         <v>0</v>
       </c>
       <c r="P44">
-        <v>21.30941234</v>
+        <v>21.12630311</v>
       </c>
       <c r="Q44">
-        <v>26.20941234</v>
+        <v>26.02630311</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1432685820140896</v>
+        <v>0.1449785571371438</v>
       </c>
       <c r="T44">
-        <v>1.899844081630907</v>
+        <v>1.933174679554256</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.770843176371778</v>
+        <v>3.683149149014294</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.108996777568172</v>
+        <v>0.109151777568172</v>
       </c>
       <c r="C45">
-        <v>157.7019547123896</v>
+        <v>154.4240133456044</v>
       </c>
       <c r="D45">
-        <v>210.9472547123895</v>
+        <v>210.6564133456044</v>
       </c>
       <c r="E45">
-        <v>122.5353</v>
+        <v>125.5224</v>
       </c>
       <c r="F45">
-        <v>128.4453</v>
+        <v>131.4324</v>
       </c>
       <c r="G45">
         <v>75.2</v>
@@ -4977,28 +4977,28 @@
         <v>29</v>
       </c>
       <c r="M45">
-        <v>7.873696890000001</v>
+        <v>8.056806120000003</v>
       </c>
       <c r="N45">
-        <v>21.12630311</v>
+        <v>20.94319388</v>
       </c>
       <c r="O45">
         <v>0</v>
       </c>
       <c r="P45">
-        <v>21.12630311</v>
+        <v>20.94319388</v>
       </c>
       <c r="Q45">
-        <v>26.02630311</v>
+        <v>25.84319387999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1449785571371438</v>
+        <v>0.1467496028003071</v>
       </c>
       <c r="T45">
-        <v>1.933174679554256</v>
+        <v>1.967695655974868</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.683149149014294</v>
+        <v>3.599441213809423</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.109151777568172</v>
+        <v>0.109306777568172</v>
       </c>
       <c r="C46">
-        <v>154.4240133456044</v>
+        <v>151.1468728637184</v>
       </c>
       <c r="D46">
-        <v>210.6564133456044</v>
+        <v>210.3663728637185</v>
       </c>
       <c r="E46">
-        <v>125.5224</v>
+        <v>128.5095</v>
       </c>
       <c r="F46">
-        <v>131.4324</v>
+        <v>134.4195</v>
       </c>
       <c r="G46">
         <v>75.2</v>
@@ -5059,28 +5059,28 @@
         <v>29</v>
       </c>
       <c r="M46">
-        <v>8.056806120000003</v>
+        <v>8.239915350000002</v>
       </c>
       <c r="N46">
-        <v>20.94319388</v>
+        <v>20.76008465</v>
       </c>
       <c r="O46">
         <v>0</v>
       </c>
       <c r="P46">
-        <v>20.94319388</v>
+        <v>20.76008465</v>
       </c>
       <c r="Q46">
-        <v>25.84319387999999</v>
+        <v>25.66008464999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1467496028003071</v>
+        <v>0.148585050123949</v>
       </c>
       <c r="T46">
-        <v>1.967695655974868</v>
+        <v>2.003471940628956</v>
       </c>
       <c r="U46">
         <v>0.0613</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.599441213809423</v>
+        <v>3.519453631280325</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.109306777568172</v>
+        <v>0.110749777568172</v>
       </c>
       <c r="C47">
-        <v>151.1468728637184</v>
+        <v>145.4974330017539</v>
       </c>
       <c r="D47">
-        <v>210.3663728637185</v>
+        <v>207.7040330017539</v>
       </c>
       <c r="E47">
-        <v>128.5095</v>
+        <v>131.4966</v>
       </c>
       <c r="F47">
-        <v>134.4195</v>
+        <v>137.4066</v>
       </c>
       <c r="G47">
         <v>75.2</v>
@@ -5141,45 +5141,45 @@
         <v>29</v>
       </c>
       <c r="M47">
-        <v>8.239915350000002</v>
+        <v>8.807763060000003</v>
       </c>
       <c r="N47">
-        <v>20.76008465</v>
+        <v>20.19223694</v>
       </c>
       <c r="O47">
         <v>0</v>
       </c>
       <c r="P47">
-        <v>20.76008465</v>
+        <v>20.19223694</v>
       </c>
       <c r="Q47">
-        <v>25.66008464999999</v>
+        <v>25.09223694</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.148585050123949</v>
+        <v>0.1504884769780962</v>
       </c>
       <c r="T47">
-        <v>2.003471940628956</v>
+        <v>2.040573272862825</v>
       </c>
       <c r="U47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V47">
         <v>0</v>
       </c>
       <c r="W47">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.519453631280325</v>
+        <v>3.292549970116929</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.110749777568172</v>
+        <v>0.110932777568172</v>
       </c>
       <c r="C48">
-        <v>145.4974330017539</v>
+        <v>142.177504595894</v>
       </c>
       <c r="D48">
-        <v>207.7040330017539</v>
+        <v>207.371204595894</v>
       </c>
       <c r="E48">
-        <v>131.4966</v>
+        <v>134.4837</v>
       </c>
       <c r="F48">
-        <v>137.4066</v>
+        <v>140.3937</v>
       </c>
       <c r="G48">
         <v>75.2</v>
@@ -5223,28 +5223,28 @@
         <v>29</v>
       </c>
       <c r="M48">
-        <v>8.807763060000003</v>
+        <v>8.999236170000001</v>
       </c>
       <c r="N48">
-        <v>20.19223694</v>
+        <v>20.00076383</v>
       </c>
       <c r="O48">
         <v>0</v>
       </c>
       <c r="P48">
-        <v>20.19223694</v>
+        <v>20.00076383</v>
       </c>
       <c r="Q48">
-        <v>25.09223694</v>
+        <v>24.90076383</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1504884769780962</v>
+        <v>0.1524637312607018</v>
       </c>
       <c r="T48">
-        <v>2.040573272862825</v>
+        <v>2.079074655369671</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.292549970116929</v>
+        <v>3.22249571543359</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.110932777568172</v>
+        <v>0.111115777568172</v>
       </c>
       <c r="C49">
-        <v>142.177504595894</v>
+        <v>138.8586411431101</v>
       </c>
       <c r="D49">
-        <v>207.371204595894</v>
+        <v>207.0394411431101</v>
       </c>
       <c r="E49">
-        <v>134.4837</v>
+        <v>137.4708</v>
       </c>
       <c r="F49">
-        <v>140.3937</v>
+        <v>143.3808</v>
       </c>
       <c r="G49">
         <v>75.2</v>
@@ -5305,28 +5305,28 @@
         <v>29</v>
       </c>
       <c r="M49">
-        <v>8.999236170000001</v>
+        <v>9.190709280000002</v>
       </c>
       <c r="N49">
-        <v>20.00076383</v>
+        <v>19.80929072</v>
       </c>
       <c r="O49">
         <v>0</v>
       </c>
       <c r="P49">
-        <v>20.00076383</v>
+        <v>19.80929072</v>
       </c>
       <c r="Q49">
-        <v>24.90076383</v>
+        <v>24.70929072</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1524637312607018</v>
+        <v>0.1545149568618692</v>
       </c>
       <c r="T49">
-        <v>2.079074655369671</v>
+        <v>2.119056860280627</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.22249571543359</v>
+        <v>3.155360388028724</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.111115777568172</v>
+        <v>0.111298777568172</v>
       </c>
       <c r="C50">
-        <v>138.8586411431101</v>
+        <v>135.5408375402614</v>
       </c>
       <c r="D50">
-        <v>207.0394411431101</v>
+        <v>206.7087375402614</v>
       </c>
       <c r="E50">
-        <v>137.4708</v>
+        <v>140.4579</v>
       </c>
       <c r="F50">
-        <v>143.3808</v>
+        <v>146.3679</v>
       </c>
       <c r="G50">
         <v>75.2</v>
@@ -5387,28 +5387,28 @@
         <v>29</v>
       </c>
       <c r="M50">
-        <v>9.190709280000002</v>
+        <v>9.382182390000002</v>
       </c>
       <c r="N50">
-        <v>19.80929072</v>
+        <v>19.61781761</v>
       </c>
       <c r="O50">
         <v>0</v>
       </c>
       <c r="P50">
-        <v>19.80929072</v>
+        <v>19.61781761</v>
       </c>
       <c r="Q50">
-        <v>24.70929072</v>
+        <v>24.51781760999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1545149568618692</v>
+        <v>0.1566466226826901</v>
       </c>
       <c r="T50">
-        <v>2.119056860280626</v>
+        <v>2.160606994795933</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.155360388028724</v>
+        <v>3.090965278068954</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.111298777568172</v>
+        <v>0.111481777568172</v>
       </c>
       <c r="C51">
-        <v>135.5408375402614</v>
+        <v>132.2240887167597</v>
       </c>
       <c r="D51">
-        <v>206.7087375402614</v>
+        <v>206.3790887167597</v>
       </c>
       <c r="E51">
-        <v>140.4579</v>
+        <v>143.445</v>
       </c>
       <c r="F51">
-        <v>146.3679</v>
+        <v>149.355</v>
       </c>
       <c r="G51">
         <v>75.2</v>
@@ -5469,28 +5469,28 @@
         <v>29</v>
       </c>
       <c r="M51">
-        <v>9.382182390000002</v>
+        <v>9.573655500000001</v>
       </c>
       <c r="N51">
-        <v>19.61781761</v>
+        <v>19.4263445</v>
       </c>
       <c r="O51">
         <v>0</v>
       </c>
       <c r="P51">
-        <v>19.61781761</v>
+        <v>19.4263445</v>
       </c>
       <c r="Q51">
-        <v>24.51781760999999</v>
+        <v>24.3263445</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1566466226826901</v>
+        <v>0.158863555136344</v>
       </c>
       <c r="T51">
-        <v>2.160606994795933</v>
+        <v>2.203819134691852</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.090965278068954</v>
+        <v>3.029145972507575</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.111481777568172</v>
+        <v>0.115642777568172</v>
       </c>
       <c r="C52">
-        <v>132.2240887167597</v>
+        <v>122.0153480621577</v>
       </c>
       <c r="D52">
-        <v>206.3790887167597</v>
+        <v>199.1574480621577</v>
       </c>
       <c r="E52">
-        <v>143.445</v>
+        <v>146.4321</v>
       </c>
       <c r="F52">
-        <v>149.355</v>
+        <v>152.3421</v>
       </c>
       <c r="G52">
         <v>75.2</v>
@@ -5551,45 +5551,45 @@
         <v>29</v>
       </c>
       <c r="M52">
-        <v>9.573655500000001</v>
+        <v>10.95339699</v>
       </c>
       <c r="N52">
-        <v>19.4263445</v>
+        <v>18.04660301</v>
       </c>
       <c r="O52">
         <v>0</v>
       </c>
       <c r="P52">
-        <v>19.4263445</v>
+        <v>18.04660301</v>
       </c>
       <c r="Q52">
-        <v>24.3263445</v>
+        <v>22.94660301</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.158863555136344</v>
+        <v>0.1611709746289224</v>
       </c>
       <c r="T52">
-        <v>2.203819134691852</v>
+        <v>2.248795035399849</v>
       </c>
       <c r="U52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V52">
         <v>0</v>
       </c>
       <c r="W52">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>3.029145972507575</v>
+        <v>2.647580474484381</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.115642777568172</v>
+        <v>0.115903777568172</v>
       </c>
       <c r="C53">
-        <v>122.0153480621577</v>
+        <v>118.5920765030595</v>
       </c>
       <c r="D53">
-        <v>199.1574480621577</v>
+        <v>198.7212765030595</v>
       </c>
       <c r="E53">
-        <v>146.4321</v>
+        <v>149.4192</v>
       </c>
       <c r="F53">
-        <v>152.3421</v>
+        <v>155.3292</v>
       </c>
       <c r="G53">
         <v>75.2</v>
@@ -5633,28 +5633,28 @@
         <v>29</v>
       </c>
       <c r="M53">
-        <v>10.95339699</v>
+        <v>11.16816948</v>
       </c>
       <c r="N53">
-        <v>18.04660301</v>
+        <v>17.83183052</v>
       </c>
       <c r="O53">
         <v>0</v>
       </c>
       <c r="P53">
-        <v>18.04660301</v>
+        <v>17.83183052</v>
       </c>
       <c r="Q53">
-        <v>22.94660301</v>
+        <v>22.73183052</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1611709746289224</v>
+        <v>0.1635745366003583</v>
       </c>
       <c r="T53">
-        <v>2.248795035399849</v>
+        <v>2.295644931970679</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.647580474484381</v>
+        <v>2.596665465359682</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.115903777568172</v>
+        <v>0.116164777568172</v>
       </c>
       <c r="C54">
-        <v>118.5920765030595</v>
+        <v>115.170711273726</v>
       </c>
       <c r="D54">
-        <v>198.7212765030595</v>
+        <v>198.2870112737261</v>
       </c>
       <c r="E54">
-        <v>149.4192</v>
+        <v>152.4063</v>
       </c>
       <c r="F54">
-        <v>155.3292</v>
+        <v>158.3163</v>
       </c>
       <c r="G54">
         <v>75.2</v>
@@ -5715,28 +5715,28 @@
         <v>29</v>
       </c>
       <c r="M54">
-        <v>11.16816948</v>
+        <v>11.38294197</v>
       </c>
       <c r="N54">
-        <v>17.83183052</v>
+        <v>17.61705803</v>
       </c>
       <c r="O54">
         <v>0</v>
       </c>
       <c r="P54">
-        <v>17.83183052</v>
+        <v>17.61705803</v>
       </c>
       <c r="Q54">
-        <v>22.73183052</v>
+        <v>22.51705802999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1635745366003583</v>
+        <v>0.1660803778046212</v>
       </c>
       <c r="T54">
-        <v>2.295644931970679</v>
+        <v>2.344488441161544</v>
       </c>
       <c r="U54">
         <v>0.07190000000000001</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.596665465359682</v>
+        <v>2.547671777334027</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.116164777568172</v>
+        <v>0.116425777568172</v>
       </c>
       <c r="C55">
-        <v>115.170711273726</v>
+        <v>111.7512399037124</v>
       </c>
       <c r="D55">
-        <v>198.2870112737261</v>
+        <v>197.8546399037125</v>
       </c>
       <c r="E55">
-        <v>152.4063</v>
+        <v>155.3934</v>
       </c>
       <c r="F55">
-        <v>158.3163</v>
+        <v>161.3034</v>
       </c>
       <c r="G55">
         <v>75.2</v>
@@ -5797,28 +5797,28 @@
         <v>29</v>
       </c>
       <c r="M55">
-        <v>11.38294197</v>
+        <v>11.59771446</v>
       </c>
       <c r="N55">
-        <v>17.61705803</v>
+        <v>17.40228553999999</v>
       </c>
       <c r="O55">
         <v>0</v>
       </c>
       <c r="P55">
-        <v>17.61705803</v>
+        <v>17.40228553999999</v>
       </c>
       <c r="Q55">
-        <v>22.51705802999999</v>
+        <v>22.30228553999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1660803778046212</v>
+        <v>0.1686951686264608</v>
       </c>
       <c r="T55">
-        <v>2.344488441161544</v>
+        <v>2.395455581186795</v>
       </c>
       <c r="U55">
         <v>0.07190000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.547671777334027</v>
+        <v>2.50049267034636</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.116425777568172</v>
+        <v>0.118831777568172</v>
       </c>
       <c r="C56">
-        <v>111.7512399037124</v>
+        <v>104.8654307153993</v>
       </c>
       <c r="D56">
-        <v>197.8546399037125</v>
+        <v>193.9559307153993</v>
       </c>
       <c r="E56">
-        <v>155.3934</v>
+        <v>158.3805</v>
       </c>
       <c r="F56">
-        <v>161.3034</v>
+        <v>164.2905</v>
       </c>
       <c r="G56">
         <v>75.2</v>
@@ -5879,45 +5879,45 @@
         <v>29</v>
       </c>
       <c r="M56">
-        <v>11.59771446</v>
+        <v>12.4532199</v>
       </c>
       <c r="N56">
-        <v>17.40228553999999</v>
+        <v>16.5467801</v>
       </c>
       <c r="O56">
         <v>0</v>
       </c>
       <c r="P56">
-        <v>17.40228553999999</v>
+        <v>16.5467801</v>
       </c>
       <c r="Q56">
-        <v>22.30228553999999</v>
+        <v>21.44678009999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1686951686264608</v>
+        <v>0.1714261723737155</v>
       </c>
       <c r="T56">
-        <v>2.395455581186795</v>
+        <v>2.448687927435391</v>
       </c>
       <c r="U56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V56">
         <v>0</v>
       </c>
       <c r="W56">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y56">
-        <v>2.50049267034636</v>
+        <v>2.328715001651902</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.118831777568172</v>
+        <v>0.119131777568172</v>
       </c>
       <c r="C57">
-        <v>104.8654307153993</v>
+        <v>101.4029543815247</v>
       </c>
       <c r="D57">
-        <v>193.9559307153993</v>
+        <v>193.4805543815247</v>
       </c>
       <c r="E57">
-        <v>158.3805</v>
+        <v>161.3676</v>
       </c>
       <c r="F57">
-        <v>164.2905</v>
+        <v>167.2776</v>
       </c>
       <c r="G57">
         <v>75.2</v>
@@ -5961,28 +5961,28 @@
         <v>29</v>
       </c>
       <c r="M57">
-        <v>12.4532199</v>
+        <v>12.67964208</v>
       </c>
       <c r="N57">
-        <v>16.5467801</v>
+        <v>16.32035792</v>
       </c>
       <c r="O57">
         <v>0</v>
       </c>
       <c r="P57">
-        <v>16.5467801</v>
+        <v>16.32035792</v>
       </c>
       <c r="Q57">
-        <v>21.44678009999999</v>
+        <v>21.22035791999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1714261723737155</v>
+        <v>0.1742813126549363</v>
       </c>
       <c r="T57">
-        <v>2.448687927435391</v>
+        <v>2.504339925786195</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.328715001651902</v>
+        <v>2.287130805193832</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.119131777568172</v>
+        <v>0.119431777568172</v>
       </c>
       <c r="C58">
-        <v>101.4029543815247</v>
+        <v>97.94280259776744</v>
       </c>
       <c r="D58">
-        <v>193.4805543815247</v>
+        <v>193.0075025977675</v>
       </c>
       <c r="E58">
-        <v>161.3676</v>
+        <v>164.3547</v>
       </c>
       <c r="F58">
-        <v>167.2776</v>
+        <v>170.2647</v>
       </c>
       <c r="G58">
         <v>75.2</v>
@@ -6043,28 +6043,28 @@
         <v>29</v>
       </c>
       <c r="M58">
-        <v>12.67964208</v>
+        <v>12.90606426</v>
       </c>
       <c r="N58">
-        <v>16.32035792</v>
+        <v>16.09393574</v>
       </c>
       <c r="O58">
         <v>0</v>
       </c>
       <c r="P58">
-        <v>16.32035792</v>
+        <v>16.09393574</v>
       </c>
       <c r="Q58">
-        <v>21.22035791999999</v>
+        <v>20.99393573999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1742813126549363</v>
+        <v>0.1772692501585395</v>
       </c>
       <c r="T58">
-        <v>2.504339925786195</v>
+        <v>2.562580389176572</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.287130805193832</v>
+        <v>2.247005703348326</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.119431777568172</v>
+        <v>0.119731777568172</v>
       </c>
       <c r="C59">
-        <v>97.94280259776744</v>
+        <v>94.4849583554325</v>
       </c>
       <c r="D59">
-        <v>193.0075025977675</v>
+        <v>192.5367583554325</v>
       </c>
       <c r="E59">
-        <v>164.3547</v>
+        <v>167.3418</v>
       </c>
       <c r="F59">
-        <v>170.2647</v>
+        <v>173.2518</v>
       </c>
       <c r="G59">
         <v>75.2</v>
@@ -6125,28 +6125,28 @@
         <v>29</v>
       </c>
       <c r="M59">
-        <v>12.90606426</v>
+        <v>13.13248644</v>
       </c>
       <c r="N59">
-        <v>16.09393574</v>
+        <v>15.86751356</v>
       </c>
       <c r="O59">
         <v>0</v>
       </c>
       <c r="P59">
-        <v>16.09393574</v>
+        <v>15.86751356</v>
       </c>
       <c r="Q59">
-        <v>20.99393573999999</v>
+        <v>20.76751356</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1772692501585395</v>
+        <v>0.1803994704004095</v>
       </c>
       <c r="T59">
-        <v>2.562580389176572</v>
+        <v>2.62359420796649</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.247005703348326</v>
+        <v>2.208264225704389</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.119731777568172</v>
+        <v>0.120031777568172</v>
       </c>
       <c r="C60">
-        <v>94.48495835543252</v>
+        <v>91.02940481135755</v>
       </c>
       <c r="D60">
-        <v>192.5367583554325</v>
+        <v>192.0683048113576</v>
       </c>
       <c r="E60">
-        <v>167.3418</v>
+        <v>170.3289</v>
       </c>
       <c r="F60">
-        <v>173.2518</v>
+        <v>176.2389</v>
       </c>
       <c r="G60">
         <v>75.2</v>
@@ -6207,28 +6207,28 @@
         <v>29</v>
       </c>
       <c r="M60">
-        <v>13.13248644</v>
+        <v>13.35890862</v>
       </c>
       <c r="N60">
-        <v>15.86751356</v>
+        <v>15.64109138</v>
       </c>
       <c r="O60">
         <v>0</v>
       </c>
       <c r="P60">
-        <v>15.86751356</v>
+        <v>15.64109138</v>
       </c>
       <c r="Q60">
-        <v>20.76751356</v>
+        <v>20.54109138</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1803994704004094</v>
+        <v>0.1836823843126145</v>
       </c>
       <c r="T60">
-        <v>2.62359420796649</v>
+        <v>2.687584310599819</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.20826422570439</v>
+        <v>2.170836018489061</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.120031777568172</v>
+        <v>0.120331777568172</v>
       </c>
       <c r="C61">
-        <v>91.02940481135755</v>
+        <v>87.57612528590417</v>
       </c>
       <c r="D61">
-        <v>192.0683048113576</v>
+        <v>191.6021252859042</v>
       </c>
       <c r="E61">
-        <v>170.3289</v>
+        <v>173.316</v>
       </c>
       <c r="F61">
-        <v>176.2389</v>
+        <v>179.226</v>
       </c>
       <c r="G61">
         <v>75.2</v>
@@ -6289,28 +6289,28 @@
         <v>29</v>
       </c>
       <c r="M61">
-        <v>13.35890862</v>
+        <v>13.5853308</v>
       </c>
       <c r="N61">
-        <v>15.64109138</v>
+        <v>15.4146692</v>
       </c>
       <c r="O61">
         <v>0</v>
       </c>
       <c r="P61">
-        <v>15.64109138</v>
+        <v>15.4146692</v>
       </c>
       <c r="Q61">
-        <v>20.54109138</v>
+        <v>20.3146692</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1836823843126145</v>
+        <v>0.1871294439204299</v>
       </c>
       <c r="T61">
-        <v>2.687584310599819</v>
+        <v>2.754773918364815</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.170836018489061</v>
+        <v>2.13465541818091</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.120331777568172</v>
+        <v>0.120631777568172</v>
       </c>
       <c r="C62">
-        <v>87.57612528590417</v>
+        <v>84.12510326097802</v>
       </c>
       <c r="D62">
-        <v>191.6021252859042</v>
+        <v>191.138203260978</v>
       </c>
       <c r="E62">
-        <v>173.316</v>
+        <v>176.3031</v>
       </c>
       <c r="F62">
-        <v>179.226</v>
+        <v>182.2131</v>
       </c>
       <c r="G62">
         <v>75.2</v>
@@ -6371,28 +6371,28 @@
         <v>29</v>
       </c>
       <c r="M62">
-        <v>13.5853308</v>
+        <v>13.81175298</v>
       </c>
       <c r="N62">
-        <v>15.4146692</v>
+        <v>15.18824702</v>
       </c>
       <c r="O62">
         <v>0</v>
       </c>
       <c r="P62">
-        <v>15.4146692</v>
+        <v>15.18824702</v>
       </c>
       <c r="Q62">
-        <v>20.3146692</v>
+        <v>20.08824702</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1871294439204299</v>
+        <v>0.1907532758158256</v>
       </c>
       <c r="T62">
-        <v>2.754773918364815</v>
+        <v>2.825409147040835</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.13465541818091</v>
+        <v>2.09966106706319</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.120631777568172</v>
+        <v>0.120931777568172</v>
       </c>
       <c r="C63">
-        <v>84.12510326097802</v>
+        <v>80.67632237807797</v>
       </c>
       <c r="D63">
-        <v>191.138203260978</v>
+        <v>190.676522378078</v>
       </c>
       <c r="E63">
-        <v>176.3031</v>
+        <v>179.2902</v>
       </c>
       <c r="F63">
-        <v>182.2131</v>
+        <v>185.2002</v>
       </c>
       <c r="G63">
         <v>75.2</v>
@@ -6453,28 +6453,28 @@
         <v>29</v>
       </c>
       <c r="M63">
-        <v>13.81175298</v>
+        <v>14.03817516</v>
       </c>
       <c r="N63">
-        <v>15.18824702</v>
+        <v>14.96182484</v>
       </c>
       <c r="O63">
         <v>0</v>
       </c>
       <c r="P63">
-        <v>15.18824702</v>
+        <v>14.96182484</v>
       </c>
       <c r="Q63">
-        <v>20.08824702</v>
+        <v>19.86182484</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1907532758158256</v>
+        <v>0.1945678357057157</v>
       </c>
       <c r="T63">
-        <v>2.825409147040835</v>
+        <v>2.899762019331384</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.09966106706319</v>
+        <v>2.065795565981525</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.120931777568172</v>
+        <v>0.121231777568172</v>
       </c>
       <c r="C64">
-        <v>80.67632237807797</v>
+        <v>77.22976643637341</v>
       </c>
       <c r="D64">
-        <v>190.676522378078</v>
+        <v>190.2170664363734</v>
       </c>
       <c r="E64">
-        <v>179.2902</v>
+        <v>182.2773</v>
       </c>
       <c r="F64">
-        <v>185.2002</v>
+        <v>188.1873</v>
       </c>
       <c r="G64">
         <v>75.2</v>
@@ -6535,28 +6535,28 @@
         <v>29</v>
       </c>
       <c r="M64">
-        <v>14.03817516</v>
+        <v>14.26459734</v>
       </c>
       <c r="N64">
-        <v>14.96182484</v>
+        <v>14.73540266</v>
       </c>
       <c r="O64">
         <v>0</v>
       </c>
       <c r="P64">
-        <v>14.96182484</v>
+        <v>14.73540266</v>
       </c>
       <c r="Q64">
-        <v>19.86182484</v>
+        <v>19.63540266</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1945678357057157</v>
+        <v>0.1985885880220864</v>
       </c>
       <c r="T64">
-        <v>2.899762019331384</v>
+        <v>2.978133965799799</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.065795565981525</v>
+        <v>2.033005160172295</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.121231777568172</v>
+        <v>0.121531777568172</v>
       </c>
       <c r="C65">
-        <v>77.22976643637341</v>
+        <v>73.78541939080881</v>
       </c>
       <c r="D65">
-        <v>190.2170664363734</v>
+        <v>189.7598193908088</v>
       </c>
       <c r="E65">
-        <v>182.2773</v>
+        <v>185.2644</v>
       </c>
       <c r="F65">
-        <v>188.1873</v>
+        <v>191.1744</v>
       </c>
       <c r="G65">
         <v>75.2</v>
@@ -6617,28 +6617,28 @@
         <v>29</v>
       </c>
       <c r="M65">
-        <v>14.26459734</v>
+        <v>14.49101952</v>
       </c>
       <c r="N65">
-        <v>14.73540266</v>
+        <v>14.50898048</v>
       </c>
       <c r="O65">
         <v>0</v>
       </c>
       <c r="P65">
-        <v>14.73540266</v>
+        <v>14.50898048</v>
       </c>
       <c r="Q65">
-        <v>19.63540266</v>
+        <v>19.40898048</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1985885880220864</v>
+        <v>0.2028327154671444</v>
       </c>
       <c r="T65">
-        <v>2.978133965799799</v>
+        <v>3.060859909294238</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.033005160172295</v>
+        <v>2.001239454544603</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.121531777568172</v>
+        <v>0.131061777568172</v>
       </c>
       <c r="C66">
-        <v>73.78541939080881</v>
+        <v>57.33601905823323</v>
       </c>
       <c r="D66">
-        <v>189.7598193908088</v>
+        <v>176.2975190582333</v>
       </c>
       <c r="E66">
-        <v>185.2644</v>
+        <v>188.2515</v>
       </c>
       <c r="F66">
-        <v>191.1744</v>
+        <v>194.1615</v>
       </c>
       <c r="G66">
         <v>75.2</v>
@@ -6699,45 +6699,45 @@
         <v>29</v>
       </c>
       <c r="M66">
-        <v>14.49101952</v>
+        <v>17.474535</v>
       </c>
       <c r="N66">
-        <v>14.50898048</v>
+        <v>11.525465</v>
       </c>
       <c r="O66">
         <v>0</v>
       </c>
       <c r="P66">
-        <v>14.50898048</v>
+        <v>11.525465</v>
       </c>
       <c r="Q66">
-        <v>19.40898048</v>
+        <v>16.425465</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2028327154671444</v>
+        <v>0.2073193644804914</v>
       </c>
       <c r="T66">
-        <v>3.060859909294238</v>
+        <v>3.148313049559789</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0</v>
       </c>
       <c r="W66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.001239454544603</v>
+        <v>1.659557750749877</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.131061777568172</v>
+        <v>0.131503777568172</v>
       </c>
       <c r="C67">
-        <v>57.33601905823323</v>
+        <v>53.77073788822423</v>
       </c>
       <c r="D67">
-        <v>176.2975190582333</v>
+        <v>175.7193378882243</v>
       </c>
       <c r="E67">
-        <v>188.2515</v>
+        <v>191.2386</v>
       </c>
       <c r="F67">
-        <v>194.1615</v>
+        <v>197.1486</v>
       </c>
       <c r="G67">
         <v>75.2</v>
@@ -6781,28 +6781,28 @@
         <v>29</v>
       </c>
       <c r="M67">
-        <v>17.474535</v>
+        <v>17.743374</v>
       </c>
       <c r="N67">
-        <v>11.525465</v>
+        <v>11.256626</v>
       </c>
       <c r="O67">
         <v>0</v>
       </c>
       <c r="P67">
-        <v>11.525465</v>
+        <v>11.256626</v>
       </c>
       <c r="Q67">
-        <v>16.425465</v>
+        <v>16.156626</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2073193644804914</v>
+        <v>0.2120699340240352</v>
       </c>
       <c r="T67">
-        <v>3.148313049559789</v>
+        <v>3.2409104921939</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.659557750749877</v>
+        <v>1.634412936344575</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.131503777568172</v>
+        <v>0.131945777568172</v>
       </c>
       <c r="C68">
-        <v>53.77073788822423</v>
+        <v>50.20923670003214</v>
       </c>
       <c r="D68">
-        <v>175.7193378882243</v>
+        <v>175.1449367000322</v>
       </c>
       <c r="E68">
-        <v>191.2386</v>
+        <v>194.2257</v>
       </c>
       <c r="F68">
-        <v>197.1486</v>
+        <v>200.1357</v>
       </c>
       <c r="G68">
         <v>75.2</v>
@@ -6863,28 +6863,28 @@
         <v>29</v>
       </c>
       <c r="M68">
-        <v>17.743374</v>
+        <v>18.012213</v>
       </c>
       <c r="N68">
-        <v>11.256626</v>
+        <v>10.987787</v>
       </c>
       <c r="O68">
         <v>0</v>
       </c>
       <c r="P68">
-        <v>11.256626</v>
+        <v>10.987787</v>
       </c>
       <c r="Q68">
-        <v>16.156626</v>
+        <v>15.887787</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2120699340240352</v>
+        <v>0.2171084168732484</v>
       </c>
       <c r="T68">
-        <v>3.2409104921939</v>
+        <v>3.339119901048261</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.634412936344575</v>
+        <v>1.61001871341406</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.131945777568172</v>
+        <v>0.132387777568172</v>
       </c>
       <c r="C69">
-        <v>50.20923670003214</v>
+        <v>46.65147854578692</v>
       </c>
       <c r="D69">
-        <v>175.1449367000322</v>
+        <v>174.574278545787</v>
       </c>
       <c r="E69">
-        <v>194.2257</v>
+        <v>197.2128</v>
       </c>
       <c r="F69">
-        <v>200.1357</v>
+        <v>203.1228</v>
       </c>
       <c r="G69">
         <v>75.2</v>
@@ -6945,28 +6945,28 @@
         <v>29</v>
       </c>
       <c r="M69">
-        <v>18.012213</v>
+        <v>18.281052</v>
       </c>
       <c r="N69">
-        <v>10.987787</v>
+        <v>10.718948</v>
       </c>
       <c r="O69">
         <v>0</v>
       </c>
       <c r="P69">
-        <v>10.987787</v>
+        <v>10.718948</v>
       </c>
       <c r="Q69">
-        <v>15.887787</v>
+        <v>15.618948</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2171084168732484</v>
+        <v>0.2224618049005375</v>
       </c>
       <c r="T69">
-        <v>3.339119901048261</v>
+        <v>3.443467397956019</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.61001871341406</v>
+        <v>1.586341967628559</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.132387777568172</v>
+        <v>0.132829777568172</v>
       </c>
       <c r="C70">
-        <v>46.65147854578692</v>
+        <v>43.09742695758985</v>
       </c>
       <c r="D70">
-        <v>174.574278545787</v>
+        <v>174.0073269575899</v>
       </c>
       <c r="E70">
-        <v>197.2128</v>
+        <v>200.1999</v>
       </c>
       <c r="F70">
-        <v>203.1228</v>
+        <v>206.1099</v>
       </c>
       <c r="G70">
         <v>75.2</v>
@@ -7027,28 +7027,28 @@
         <v>29</v>
       </c>
       <c r="M70">
-        <v>18.281052</v>
+        <v>18.549891</v>
       </c>
       <c r="N70">
-        <v>10.718948</v>
+        <v>10.450109</v>
       </c>
       <c r="O70">
         <v>0</v>
       </c>
       <c r="P70">
-        <v>10.718948</v>
+        <v>10.450109</v>
       </c>
       <c r="Q70">
-        <v>15.618948</v>
+        <v>15.350109</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2224618049005375</v>
+        <v>0.2281605728005548</v>
       </c>
       <c r="T70">
-        <v>3.443467397956019</v>
+        <v>3.554546991438471</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.586341967628559</v>
+        <v>1.563351504329594</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.132829777568172</v>
+        <v>0.133271777568172</v>
       </c>
       <c r="C71">
-        <v>43.09742695758985</v>
+        <v>39.54704593974469</v>
       </c>
       <c r="D71">
-        <v>174.0073269575899</v>
+        <v>173.4440459397447</v>
       </c>
       <c r="E71">
-        <v>200.1999</v>
+        <v>203.187</v>
       </c>
       <c r="F71">
-        <v>206.1099</v>
+        <v>209.097</v>
       </c>
       <c r="G71">
         <v>75.2</v>
@@ -7109,28 +7109,28 @@
         <v>29</v>
       </c>
       <c r="M71">
-        <v>18.549891</v>
+        <v>18.81873</v>
       </c>
       <c r="N71">
-        <v>10.450109</v>
+        <v>10.18127</v>
       </c>
       <c r="O71">
         <v>0</v>
       </c>
       <c r="P71">
-        <v>10.450109</v>
+        <v>10.18127</v>
       </c>
       <c r="Q71">
-        <v>15.350109</v>
+        <v>15.08127</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2281605728005548</v>
+        <v>0.2342392585605733</v>
       </c>
       <c r="T71">
-        <v>3.554546991438471</v>
+        <v>3.673031891153087</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.563351504329594</v>
+        <v>1.5410179114106</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.133271777568172</v>
+        <v>0.133713777568172</v>
       </c>
       <c r="C72">
-        <v>39.54704593974469</v>
+        <v>36.00029996113938</v>
       </c>
       <c r="D72">
-        <v>173.4440459397447</v>
+        <v>172.8843999611394</v>
       </c>
       <c r="E72">
-        <v>203.187</v>
+        <v>206.1741</v>
       </c>
       <c r="F72">
-        <v>209.097</v>
+        <v>212.0841</v>
       </c>
       <c r="G72">
         <v>75.2</v>
@@ -7191,28 +7191,28 @@
         <v>29</v>
       </c>
       <c r="M72">
-        <v>18.81873</v>
+        <v>19.087569</v>
       </c>
       <c r="N72">
-        <v>10.18127</v>
+        <v>9.912430999999998</v>
       </c>
       <c r="O72">
         <v>0</v>
       </c>
       <c r="P72">
-        <v>10.18127</v>
+        <v>9.912430999999998</v>
       </c>
       <c r="Q72">
-        <v>15.08127</v>
+        <v>14.812431</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2342392585605733</v>
+        <v>0.2407371640281793</v>
       </c>
       <c r="T72">
-        <v>3.673031891153087</v>
+        <v>3.799688163261814</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.5410179114106</v>
+        <v>1.519313433785098</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.133713777568172</v>
+        <v>0.175051777568172</v>
       </c>
       <c r="C73">
-        <v>36.0002999611394</v>
+        <v>-7.064385088688908</v>
       </c>
       <c r="D73">
-        <v>172.8843999611394</v>
+        <v>132.8068149113111</v>
       </c>
       <c r="E73">
-        <v>206.1741</v>
+        <v>209.1612</v>
       </c>
       <c r="F73">
-        <v>212.0841</v>
+        <v>215.0712</v>
       </c>
       <c r="G73">
         <v>75.2</v>
@@ -7273,45 +7273,45 @@
         <v>29</v>
       </c>
       <c r="M73">
-        <v>19.087569</v>
+        <v>31.57245216</v>
       </c>
       <c r="N73">
-        <v>9.912431000000002</v>
+        <v>-2.572452160000005</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P73">
-        <v>9.912431000000002</v>
+        <v>-2.572452160000005</v>
       </c>
       <c r="Q73">
-        <v>14.812431</v>
+        <v>2.327547839999994</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2407371640281792</v>
+        <v>0.2476992056006142</v>
       </c>
       <c r="T73">
-        <v>3.799688163261813</v>
+        <v>3.935391311949735</v>
       </c>
       <c r="U73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V73">
         <v>0</v>
       </c>
       <c r="W73">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.519313433785099</v>
+        <v>0.9185222564606776</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.175051777568172</v>
+        <v>0.176061777568172</v>
       </c>
       <c r="C74">
-        <v>-7.064385088688908</v>
+        <v>-10.79945674187229</v>
       </c>
       <c r="D74">
-        <v>132.8068149113111</v>
+        <v>132.0588432581278</v>
       </c>
       <c r="E74">
-        <v>209.1612</v>
+        <v>212.1483</v>
       </c>
       <c r="F74">
-        <v>215.0712</v>
+        <v>218.0583</v>
       </c>
       <c r="G74">
         <v>75.2</v>
@@ -7355,28 +7355,28 @@
         <v>29</v>
       </c>
       <c r="M74">
-        <v>31.57245216</v>
+        <v>32.01095844000001</v>
       </c>
       <c r="N74">
-        <v>-2.572452160000005</v>
+        <v>-3.01095844000001</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-2.572452160000005</v>
+        <v>-3.01095844000001</v>
       </c>
       <c r="Q74">
-        <v>2.327547839999994</v>
+        <v>1.889041559999988</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2476992056006142</v>
+        <v>0.2551769539561924</v>
       </c>
       <c r="T74">
-        <v>3.935391311949735</v>
+        <v>4.081146545725651</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.9185222564606776</v>
+        <v>0.9059397597968326</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.176061777568172</v>
+        <v>0.177071777568172</v>
       </c>
       <c r="C75">
-        <v>-10.79945674187229</v>
+        <v>-14.52615038617472</v>
       </c>
       <c r="D75">
-        <v>132.0588432581278</v>
+        <v>131.3192496138253</v>
       </c>
       <c r="E75">
-        <v>212.1483</v>
+        <v>215.1354</v>
       </c>
       <c r="F75">
-        <v>218.0583</v>
+        <v>221.0454</v>
       </c>
       <c r="G75">
         <v>75.2</v>
@@ -7437,28 +7437,28 @@
         <v>29</v>
       </c>
       <c r="M75">
-        <v>32.01095844000001</v>
+        <v>32.44946472000001</v>
       </c>
       <c r="N75">
-        <v>-3.01095844000001</v>
+        <v>-3.449464720000009</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-3.01095844000001</v>
+        <v>-3.449464720000009</v>
       </c>
       <c r="Q75">
-        <v>1.889041559999988</v>
+        <v>1.45053527999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2551769539561924</v>
+        <v>0.2632299137237383</v>
       </c>
       <c r="T75">
-        <v>4.081146545725651</v>
+        <v>4.238113720561253</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.9059397597968326</v>
+        <v>0.8936973306103889</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.177071777568172</v>
+        <v>0.178081777568172</v>
       </c>
       <c r="C76">
-        <v>-14.52615038617472</v>
+        <v>-18.2446060004001</v>
       </c>
       <c r="D76">
-        <v>131.3192496138253</v>
+        <v>130.5878939995999</v>
       </c>
       <c r="E76">
-        <v>215.1354</v>
+        <v>218.1225</v>
       </c>
       <c r="F76">
-        <v>221.0454</v>
+        <v>224.0325</v>
       </c>
       <c r="G76">
         <v>75.2</v>
@@ -7519,28 +7519,28 @@
         <v>29</v>
       </c>
       <c r="M76">
-        <v>32.44946472000001</v>
+        <v>32.88797100000001</v>
       </c>
       <c r="N76">
-        <v>-3.449464720000009</v>
+        <v>-3.887971000000007</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-3.449464720000009</v>
+        <v>-3.887971000000007</v>
       </c>
       <c r="Q76">
-        <v>1.45053527999999</v>
+        <v>1.012028999999991</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2632299137237383</v>
+        <v>0.2719271102726879</v>
       </c>
       <c r="T76">
-        <v>4.238113720561253</v>
+        <v>4.407638269383703</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8936973306103889</v>
+        <v>0.8817813662022504</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.178081777568172</v>
+        <v>0.179091777568172</v>
       </c>
       <c r="C77">
-        <v>-18.2446060004001</v>
+        <v>-21.95496046229016</v>
       </c>
       <c r="D77">
-        <v>130.5878939995999</v>
+        <v>129.8646395377098</v>
       </c>
       <c r="E77">
-        <v>218.1225</v>
+        <v>221.1096</v>
       </c>
       <c r="F77">
-        <v>224.0325</v>
+        <v>227.0196</v>
       </c>
       <c r="G77">
         <v>75.2</v>
@@ -7601,28 +7601,28 @@
         <v>29</v>
       </c>
       <c r="M77">
-        <v>32.88797100000001</v>
+        <v>33.32647728000001</v>
       </c>
       <c r="N77">
-        <v>-3.887971000000007</v>
+        <v>-4.326477280000006</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-3.887971000000007</v>
+        <v>-4.326477280000006</v>
       </c>
       <c r="Q77">
-        <v>1.012028999999991</v>
+        <v>0.5735227199999926</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2719271102726879</v>
+        <v>0.2813490732007166</v>
       </c>
       <c r="T77">
-        <v>4.407638269383703</v>
+        <v>4.591289863941358</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8817813662022504</v>
+        <v>0.8701789798048525</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.179091777568172</v>
+        <v>0.180101777568172</v>
       </c>
       <c r="C78">
-        <v>-21.95496046229016</v>
+        <v>-25.65734763392703</v>
       </c>
       <c r="D78">
-        <v>129.8646395377098</v>
+        <v>129.149352366073</v>
       </c>
       <c r="E78">
-        <v>221.1096</v>
+        <v>224.0967</v>
       </c>
       <c r="F78">
-        <v>227.0196</v>
+        <v>230.0067</v>
       </c>
       <c r="G78">
         <v>75.2</v>
@@ -7683,28 +7683,28 @@
         <v>29</v>
       </c>
       <c r="M78">
-        <v>33.32647728000001</v>
+        <v>33.76498356</v>
       </c>
       <c r="N78">
-        <v>-4.326477280000006</v>
+        <v>-4.764983560000005</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-4.326477280000006</v>
+        <v>-4.764983560000005</v>
       </c>
       <c r="Q78">
-        <v>0.5735227199999926</v>
+        <v>0.135016439999994</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2813490732007166</v>
+        <v>0.2915903372529216</v>
       </c>
       <c r="T78">
-        <v>4.591289863941358</v>
+        <v>4.79091116237359</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8701789798048525</v>
+        <v>0.8588779540931012</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.180101777568172</v>
+        <v>0.181111777568172</v>
       </c>
       <c r="C79">
-        <v>-25.65734763392703</v>
+        <v>-29.35189844432821</v>
       </c>
       <c r="D79">
-        <v>129.149352366073</v>
+        <v>128.4419015556718</v>
       </c>
       <c r="E79">
-        <v>224.0967</v>
+        <v>227.0838000000001</v>
       </c>
       <c r="F79">
-        <v>230.0067</v>
+        <v>232.9938</v>
       </c>
       <c r="G79">
         <v>75.2</v>
@@ -7765,28 +7765,28 @@
         <v>29</v>
       </c>
       <c r="M79">
-        <v>33.76498356</v>
+        <v>34.20348984000001</v>
       </c>
       <c r="N79">
-        <v>-4.764983560000005</v>
+        <v>-5.20348984000001</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-4.764983560000005</v>
+        <v>-5.20348984000001</v>
       </c>
       <c r="Q79">
-        <v>0.135016439999994</v>
+        <v>-0.3034898400000117</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2915903372529216</v>
+        <v>0.3027626253098726</v>
       </c>
       <c r="T79">
-        <v>4.79091116237359</v>
+        <v>5.00867985157239</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8588779540931012</v>
+        <v>0.8478666982713946</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.181111777568172</v>
+        <v>0.182121777568172</v>
       </c>
       <c r="C80">
-        <v>-29.35189844432821</v>
+        <v>-33.0387409693428</v>
       </c>
       <c r="D80">
-        <v>128.4419015556718</v>
+        <v>127.7421590306572</v>
       </c>
       <c r="E80">
-        <v>227.0838000000001</v>
+        <v>230.0709000000001</v>
       </c>
       <c r="F80">
-        <v>232.9938</v>
+        <v>235.9809</v>
       </c>
       <c r="G80">
         <v>75.2</v>
@@ -7847,28 +7847,28 @@
         <v>29</v>
       </c>
       <c r="M80">
-        <v>34.20348984000001</v>
+        <v>34.64199612000001</v>
       </c>
       <c r="N80">
-        <v>-5.20348984000001</v>
+        <v>-5.641996120000009</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-5.20348984000001</v>
+        <v>-5.641996120000009</v>
       </c>
       <c r="Q80">
-        <v>-0.3034898400000117</v>
+        <v>-0.7419961200000103</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3027626253098726</v>
+        <v>0.314998940800819</v>
       </c>
       <c r="T80">
-        <v>5.00867985157239</v>
+        <v>5.247188415932981</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8478666982713946</v>
+        <v>0.837134208419858</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.182121777568172</v>
+        <v>0.183131777568172</v>
       </c>
       <c r="C81">
-        <v>-33.0387409693428</v>
+        <v>-36.71800050894939</v>
       </c>
       <c r="D81">
-        <v>127.7421590306572</v>
+        <v>127.0499994910507</v>
       </c>
       <c r="E81">
-        <v>230.0709000000001</v>
+        <v>233.058</v>
       </c>
       <c r="F81">
-        <v>235.9809</v>
+        <v>238.968</v>
       </c>
       <c r="G81">
         <v>75.2</v>
@@ -7929,28 +7929,28 @@
         <v>29</v>
       </c>
       <c r="M81">
-        <v>34.64199612000001</v>
+        <v>35.08050240000001</v>
       </c>
       <c r="N81">
-        <v>-5.641996120000009</v>
+        <v>-6.080502400000007</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-5.641996120000009</v>
+        <v>-6.080502400000007</v>
       </c>
       <c r="Q81">
-        <v>-0.7419961200000103</v>
+        <v>-1.180502400000009</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.314998940800819</v>
+        <v>0.3284588878408599</v>
       </c>
       <c r="T81">
-        <v>5.247188415932981</v>
+        <v>5.50954783672963</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.837134208419858</v>
+        <v>0.8266700308146098</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.183131777568172</v>
+        <v>0.184141777568172</v>
       </c>
       <c r="C82">
-        <v>-36.71800050894939</v>
+        <v>-40.38979966205491</v>
       </c>
       <c r="D82">
-        <v>127.0499994910507</v>
+        <v>126.3653003379451</v>
       </c>
       <c r="E82">
-        <v>233.058</v>
+        <v>236.0451</v>
       </c>
       <c r="F82">
-        <v>238.968</v>
+        <v>241.9551</v>
       </c>
       <c r="G82">
         <v>75.2</v>
@@ -8011,28 +8011,28 @@
         <v>29</v>
       </c>
       <c r="M82">
-        <v>35.08050240000001</v>
+        <v>35.51900868000001</v>
       </c>
       <c r="N82">
-        <v>-6.080502400000007</v>
+        <v>-6.519008680000013</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-6.080502400000007</v>
+        <v>-6.519008680000013</v>
       </c>
       <c r="Q82">
-        <v>-1.180502400000009</v>
+        <v>-1.619008680000015</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3284588878408599</v>
+        <v>0.3433356714114315</v>
       </c>
       <c r="T82">
-        <v>5.50954783672963</v>
+        <v>5.799524038662769</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8266700308146098</v>
+        <v>0.8164642279650466</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.184141777568172</v>
+        <v>0.185151777568172</v>
       </c>
       <c r="C83">
-        <v>-40.38979966205491</v>
+        <v>-44.05425839888764</v>
       </c>
       <c r="D83">
-        <v>126.3653003379451</v>
+        <v>125.6879416011124</v>
       </c>
       <c r="E83">
-        <v>236.0451</v>
+        <v>239.0322</v>
       </c>
       <c r="F83">
-        <v>241.9551</v>
+        <v>244.9422</v>
       </c>
       <c r="G83">
         <v>75.2</v>
@@ -8093,28 +8093,28 @@
         <v>29</v>
       </c>
       <c r="M83">
-        <v>35.51900868000001</v>
+        <v>35.95751496000001</v>
       </c>
       <c r="N83">
-        <v>-6.519008680000013</v>
+        <v>-6.957514960000012</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-6.519008680000013</v>
+        <v>-6.957514960000012</v>
       </c>
       <c r="Q83">
-        <v>-1.619008680000015</v>
+        <v>-2.057514960000013</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3433356714114315</v>
+        <v>0.3598654309342889</v>
       </c>
       <c r="T83">
-        <v>5.799524038662769</v>
+        <v>6.121719818588478</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8164642279650466</v>
+        <v>0.8065073471362046</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.185151777568172</v>
+        <v>0.230981777568172</v>
       </c>
       <c r="C84">
-        <v>-44.05425839888764</v>
+        <v>-71.63150281377031</v>
       </c>
       <c r="D84">
-        <v>125.6879416011124</v>
+        <v>101.0977971862297</v>
       </c>
       <c r="E84">
-        <v>239.0322</v>
+        <v>242.0193</v>
       </c>
       <c r="F84">
-        <v>244.9422</v>
+        <v>247.9293</v>
       </c>
       <c r="G84">
         <v>75.2</v>
@@ -8175,45 +8175,45 @@
         <v>29</v>
       </c>
       <c r="M84">
-        <v>35.95751496000001</v>
+        <v>49.78420344000001</v>
       </c>
       <c r="N84">
-        <v>-6.957514960000012</v>
+        <v>-20.78420344000001</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-6.957514960000012</v>
+        <v>-20.78420344000001</v>
       </c>
       <c r="Q84">
-        <v>-2.057514960000013</v>
+        <v>-15.88420344000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3598654309342889</v>
+        <v>0.3783398680480706</v>
       </c>
       <c r="T84">
-        <v>6.121719818588478</v>
+        <v>6.481820984387801</v>
       </c>
       <c r="U84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V84">
         <v>0</v>
       </c>
       <c r="W84">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8065073471362046</v>
+        <v>0.5825140907386585</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.230981777568172</v>
+        <v>0.232531777568172</v>
       </c>
       <c r="C85">
-        <v>-71.63150281377031</v>
+        <v>-75.2831515193858</v>
       </c>
       <c r="D85">
-        <v>101.0977971862297</v>
+        <v>100.4332484806143</v>
       </c>
       <c r="E85">
-        <v>242.0193</v>
+        <v>245.0064000000001</v>
       </c>
       <c r="F85">
-        <v>247.9293</v>
+        <v>250.9164000000001</v>
       </c>
       <c r="G85">
         <v>75.2</v>
@@ -8257,28 +8257,28 @@
         <v>29</v>
       </c>
       <c r="M85">
-        <v>49.78420344000001</v>
+        <v>50.38401312000001</v>
       </c>
       <c r="N85">
-        <v>-20.78420344000001</v>
+        <v>-21.38401312000001</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-20.78420344000001</v>
+        <v>-21.38401312000001</v>
       </c>
       <c r="Q85">
-        <v>-15.88420344000001</v>
+        <v>-16.48401312000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3783398680480706</v>
+        <v>0.399123609801075</v>
       </c>
       <c r="T85">
-        <v>6.481820984387801</v>
+        <v>6.88693479591204</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5825140907386585</v>
+        <v>0.5755793991822459</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2325317775681719</v>
+        <v>0.234081777568172</v>
       </c>
       <c r="C86">
-        <v>-75.28315151938568</v>
+        <v>-78.926120688808</v>
       </c>
       <c r="D86">
-        <v>100.4332484806143</v>
+        <v>99.77737931119204</v>
       </c>
       <c r="E86">
-        <v>245.0064</v>
+        <v>247.9935</v>
       </c>
       <c r="F86">
-        <v>250.9164</v>
+        <v>253.9035</v>
       </c>
       <c r="G86">
         <v>75.2</v>
@@ -8339,28 +8339,28 @@
         <v>29</v>
       </c>
       <c r="M86">
-        <v>50.38401312000001</v>
+        <v>50.98382280000001</v>
       </c>
       <c r="N86">
-        <v>-21.38401312000001</v>
+        <v>-21.98382280000001</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-21.38401312000001</v>
+        <v>-21.98382280000001</v>
       </c>
       <c r="Q86">
-        <v>-16.48401312000001</v>
+        <v>-17.08382280000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3991236098010748</v>
+        <v>0.4226785171211465</v>
       </c>
       <c r="T86">
-        <v>6.886934795912035</v>
+        <v>7.346063782306172</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.575579399182246</v>
+        <v>0.5688078768389254</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.234081777568172</v>
+        <v>0.235631777568172</v>
       </c>
       <c r="C87">
-        <v>-78.926120688808</v>
+        <v>-82.56057926129557</v>
       </c>
       <c r="D87">
-        <v>99.77737931119204</v>
+        <v>99.13002073870443</v>
       </c>
       <c r="E87">
-        <v>247.9935</v>
+        <v>250.9806</v>
       </c>
       <c r="F87">
-        <v>253.9035</v>
+        <v>256.8906</v>
       </c>
       <c r="G87">
         <v>75.2</v>
@@ -8421,28 +8421,28 @@
         <v>29</v>
       </c>
       <c r="M87">
-        <v>50.98382280000001</v>
+        <v>51.58363248000001</v>
       </c>
       <c r="N87">
-        <v>-21.98382280000001</v>
+        <v>-22.58363248000001</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-21.98382280000001</v>
+        <v>-22.58363248000001</v>
       </c>
       <c r="Q87">
-        <v>-17.08382280000001</v>
+        <v>-17.68363248000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4226785171211465</v>
+        <v>0.4495984112012284</v>
       </c>
       <c r="T87">
-        <v>7.346063782306172</v>
+        <v>7.87078262389947</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5688078768389254</v>
+        <v>0.5621938317594031</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.235631777568172</v>
+        <v>0.237181777568172</v>
       </c>
       <c r="C88">
-        <v>-82.56057926129557</v>
+        <v>-86.18669182003788</v>
       </c>
       <c r="D88">
-        <v>99.13002073870443</v>
+        <v>98.49100817996214</v>
       </c>
       <c r="E88">
-        <v>250.9806</v>
+        <v>253.9677</v>
       </c>
       <c r="F88">
-        <v>256.8906</v>
+        <v>259.8777</v>
       </c>
       <c r="G88">
         <v>75.2</v>
@@ -8503,28 +8503,28 @@
         <v>29</v>
       </c>
       <c r="M88">
-        <v>51.58363248000001</v>
+        <v>52.18344216000001</v>
       </c>
       <c r="N88">
-        <v>-22.58363248000001</v>
+        <v>-23.18344216000001</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-22.58363248000001</v>
+        <v>-23.18344216000001</v>
       </c>
       <c r="Q88">
-        <v>-17.68363248000001</v>
+        <v>-18.28344216000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4495984112012284</v>
+        <v>0.4806598274474767</v>
       </c>
       <c r="T88">
-        <v>7.87078262389947</v>
+        <v>8.476227441122505</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5621938317594031</v>
+        <v>0.555731833693203</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.237181777568172</v>
+        <v>0.238731777568172</v>
       </c>
       <c r="C89">
-        <v>-86.18669182003788</v>
+        <v>-89.80461873165635</v>
       </c>
       <c r="D89">
-        <v>98.49100817996214</v>
+        <v>97.86018126834371</v>
       </c>
       <c r="E89">
-        <v>253.9677</v>
+        <v>256.9548</v>
       </c>
       <c r="F89">
-        <v>259.8777</v>
+        <v>262.8648000000001</v>
       </c>
       <c r="G89">
         <v>75.2</v>
@@ -8585,28 +8585,28 @@
         <v>29</v>
       </c>
       <c r="M89">
-        <v>52.18344216000001</v>
+        <v>52.78325184000001</v>
       </c>
       <c r="N89">
-        <v>-23.18344216000001</v>
+        <v>-23.78325184000001</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-23.18344216000001</v>
+        <v>-23.78325184000001</v>
       </c>
       <c r="Q89">
-        <v>-18.28344216000001</v>
+        <v>-18.88325184000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4806598274474767</v>
+        <v>0.5168981464014332</v>
       </c>
       <c r="T89">
-        <v>8.476227441122505</v>
+        <v>9.182579727882716</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.555731833693203</v>
+        <v>0.5494166992194165</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.238731777568172</v>
+        <v>0.240281777568172</v>
       </c>
       <c r="C90">
-        <v>-89.80461873165635</v>
+        <v>-93.41451628037902</v>
       </c>
       <c r="D90">
-        <v>97.86018126834371</v>
+        <v>97.23738371962102</v>
       </c>
       <c r="E90">
-        <v>256.9548</v>
+        <v>259.9419</v>
       </c>
       <c r="F90">
-        <v>262.8648000000001</v>
+        <v>265.8519000000001</v>
       </c>
       <c r="G90">
         <v>75.2</v>
@@ -8667,28 +8667,28 @@
         <v>29</v>
       </c>
       <c r="M90">
-        <v>52.78325184000001</v>
+        <v>53.38306152000001</v>
       </c>
       <c r="N90">
-        <v>-23.78325184000001</v>
+        <v>-24.38306152000001</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-23.78325184000001</v>
+        <v>-24.38306152000001</v>
       </c>
       <c r="Q90">
-        <v>-18.88325184000001</v>
+        <v>-19.48306152000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5168981464014332</v>
+        <v>0.5597252506197452</v>
       </c>
       <c r="T90">
-        <v>9.182579727882716</v>
+        <v>10.01735970314478</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5494166992194165</v>
+        <v>0.5432434778798725</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.240281777568172</v>
+        <v>0.241831777568172</v>
       </c>
       <c r="C91">
-        <v>-93.41451628037902</v>
+        <v>-97.0165367971241</v>
       </c>
       <c r="D91">
-        <v>97.23738371962102</v>
+        <v>96.62246320287593</v>
       </c>
       <c r="E91">
-        <v>259.9419</v>
+        <v>262.929</v>
       </c>
       <c r="F91">
-        <v>265.8519000000001</v>
+        <v>268.8390000000001</v>
       </c>
       <c r="G91">
         <v>75.2</v>
@@ -8749,28 +8749,28 @@
         <v>29</v>
       </c>
       <c r="M91">
-        <v>53.38306152000001</v>
+        <v>53.98287120000001</v>
       </c>
       <c r="N91">
-        <v>-24.38306152000001</v>
+        <v>-24.98287120000001</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-24.38306152000001</v>
+        <v>-24.98287120000001</v>
       </c>
       <c r="Q91">
-        <v>-19.48306152000001</v>
+        <v>-20.08287120000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5597252506197452</v>
+        <v>0.6111177756817198</v>
       </c>
       <c r="T91">
-        <v>10.01735970314478</v>
+        <v>11.01909567345926</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5432434778798725</v>
+        <v>0.5372074392367628</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.241831777568172</v>
+        <v>0.243381777568172</v>
       </c>
       <c r="C92">
-        <v>-97.0165367971241</v>
+        <v>-100.6108287837162</v>
       </c>
       <c r="D92">
-        <v>96.62246320287593</v>
+        <v>96.01527121628381</v>
       </c>
       <c r="E92">
-        <v>262.929</v>
+        <v>265.9161</v>
       </c>
       <c r="F92">
-        <v>268.8390000000001</v>
+        <v>271.8261000000001</v>
       </c>
       <c r="G92">
         <v>75.2</v>
@@ -8831,28 +8831,28 @@
         <v>29</v>
       </c>
       <c r="M92">
-        <v>53.98287120000001</v>
+        <v>54.58268088000001</v>
       </c>
       <c r="N92">
-        <v>-24.98287120000001</v>
+        <v>-25.58268088000001</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-24.98287120000001</v>
+        <v>-25.58268088000001</v>
       </c>
       <c r="Q92">
-        <v>-20.08287120000001</v>
+        <v>-20.68268088000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6111177756817198</v>
+        <v>0.6739308618685776</v>
       </c>
       <c r="T92">
-        <v>11.01909567345926</v>
+        <v>12.24343963717696</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5372074392367628</v>
+        <v>0.5313040607836116</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.243381777568172</v>
+        <v>0.244931777568172</v>
       </c>
       <c r="C93">
-        <v>-100.6108287837162</v>
+        <v>-104.1975370324485</v>
       </c>
       <c r="D93">
-        <v>96.01527121628381</v>
+        <v>95.41566296755155</v>
       </c>
       <c r="E93">
-        <v>265.9161</v>
+        <v>268.9032</v>
       </c>
       <c r="F93">
-        <v>271.8261000000001</v>
+        <v>274.8132000000001</v>
       </c>
       <c r="G93">
         <v>75.2</v>
@@ -8913,28 +8913,28 @@
         <v>29</v>
       </c>
       <c r="M93">
-        <v>54.58268088000001</v>
+        <v>55.18249056000001</v>
       </c>
       <c r="N93">
-        <v>-25.58268088000001</v>
+        <v>-26.18249056000001</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-25.58268088000001</v>
+        <v>-26.18249056000001</v>
       </c>
       <c r="Q93">
-        <v>-20.68268088000001</v>
+        <v>-21.28249056000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6739308618685776</v>
+        <v>0.75244721960215</v>
       </c>
       <c r="T93">
-        <v>12.24343963717696</v>
+        <v>13.77386959182408</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5313040607836116</v>
+        <v>0.5255290166446593</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.244931777568172</v>
+        <v>0.246481777568172</v>
       </c>
       <c r="C94">
-        <v>-104.1975370324485</v>
+        <v>-107.7768027411923</v>
       </c>
       <c r="D94">
-        <v>95.41566296755155</v>
+        <v>94.82349725880773</v>
       </c>
       <c r="E94">
-        <v>268.9032</v>
+        <v>271.8903</v>
       </c>
       <c r="F94">
-        <v>274.8132000000001</v>
+        <v>277.8003</v>
       </c>
       <c r="G94">
         <v>75.2</v>
@@ -8995,28 +8995,28 @@
         <v>29</v>
       </c>
       <c r="M94">
-        <v>55.18249056000001</v>
+        <v>55.78230024000001</v>
       </c>
       <c r="N94">
-        <v>-26.18249056000001</v>
+        <v>-26.78230024000001</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-26.18249056000001</v>
+        <v>-26.78230024000001</v>
       </c>
       <c r="Q94">
-        <v>-21.28249056000001</v>
+        <v>-21.88230024000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.75244721960215</v>
+        <v>0.8533968224024572</v>
       </c>
       <c r="T94">
-        <v>13.77386959182408</v>
+        <v>15.74156524779895</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5255290166446593</v>
+        <v>0.5198781670033188</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.246481777568172</v>
+        <v>0.248031777568172</v>
       </c>
       <c r="C95">
-        <v>-107.7768027411923</v>
+        <v>-111.3487636242475</v>
       </c>
       <c r="D95">
-        <v>94.82349725880773</v>
+        <v>94.23863637575253</v>
       </c>
       <c r="E95">
-        <v>271.8903</v>
+        <v>274.8774</v>
       </c>
       <c r="F95">
-        <v>277.8003</v>
+        <v>280.7874</v>
       </c>
       <c r="G95">
         <v>75.2</v>
@@ -9077,28 +9077,28 @@
         <v>29</v>
       </c>
       <c r="M95">
-        <v>55.78230024000001</v>
+        <v>56.38210992000001</v>
       </c>
       <c r="N95">
-        <v>-26.78230024000001</v>
+        <v>-27.38210992000001</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-26.78230024000001</v>
+        <v>-27.38210992000001</v>
       </c>
       <c r="Q95">
-        <v>-21.88230024000001</v>
+        <v>-22.48210992000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8533968224024572</v>
+        <v>0.987996292802867</v>
       </c>
       <c r="T95">
-        <v>15.74156524779895</v>
+        <v>18.36515945576545</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5198781670033188</v>
+        <v>0.5143475482054112</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.248031777568172</v>
+        <v>0.249581777568172</v>
       </c>
       <c r="C96">
-        <v>-111.3487636242475</v>
+        <v>-114.9135540191151</v>
       </c>
       <c r="D96">
-        <v>94.23863637575253</v>
+        <v>93.66094598088495</v>
       </c>
       <c r="E96">
-        <v>274.8774</v>
+        <v>277.8645</v>
       </c>
       <c r="F96">
-        <v>280.7874</v>
+        <v>283.7745</v>
       </c>
       <c r="G96">
         <v>75.2</v>
@@ -9159,28 +9159,28 @@
         <v>29</v>
       </c>
       <c r="M96">
-        <v>56.38210992000001</v>
+        <v>56.98191960000001</v>
       </c>
       <c r="N96">
-        <v>-27.38210992000001</v>
+        <v>-27.98191960000001</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-27.38210992000001</v>
+        <v>-27.98191960000001</v>
       </c>
       <c r="Q96">
-        <v>-22.48210992000001</v>
+        <v>-23.08191960000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.987996292802867</v>
+        <v>1.176435551363441</v>
       </c>
       <c r="T96">
-        <v>18.36515945576545</v>
+        <v>22.03819134691855</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5143475482054112</v>
+        <v>0.5089333634874595</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.249581777568172</v>
+        <v>0.251131777568172</v>
       </c>
       <c r="C97">
-        <v>-114.9135540191151</v>
+        <v>-118.4713049893669</v>
       </c>
       <c r="D97">
-        <v>93.66094598088495</v>
+        <v>93.09029501063314</v>
       </c>
       <c r="E97">
-        <v>277.8645</v>
+        <v>280.8516</v>
       </c>
       <c r="F97">
-        <v>283.7745</v>
+        <v>286.7616</v>
       </c>
       <c r="G97">
         <v>75.2</v>
@@ -9241,28 +9241,28 @@
         <v>29</v>
       </c>
       <c r="M97">
-        <v>56.98191960000001</v>
+        <v>57.58172928000001</v>
       </c>
       <c r="N97">
-        <v>-27.98191960000001</v>
+        <v>-28.58172928000001</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-27.98191960000001</v>
+        <v>-28.58172928000001</v>
       </c>
       <c r="Q97">
-        <v>-23.08191960000001</v>
+        <v>-23.68172928000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.176435551363441</v>
+        <v>1.459094439204302</v>
       </c>
       <c r="T97">
-        <v>22.03819134691855</v>
+        <v>27.5477391836482</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5089333634874595</v>
+        <v>0.5036319742844652</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.251131777568172</v>
+        <v>0.286631777568172</v>
       </c>
       <c r="C98">
-        <v>-118.4713049893669</v>
+        <v>-132.857812732076</v>
       </c>
       <c r="D98">
-        <v>93.09029501063317</v>
+        <v>81.69088726792404</v>
       </c>
       <c r="E98">
-        <v>280.8516</v>
+        <v>283.8387</v>
       </c>
       <c r="F98">
-        <v>286.7616</v>
+        <v>289.7487</v>
       </c>
       <c r="G98">
         <v>75.2</v>
@@ -9323,45 +9323,45 @@
         <v>29</v>
       </c>
       <c r="M98">
-        <v>57.58172928000001</v>
+        <v>68.32274346000001</v>
       </c>
       <c r="N98">
-        <v>-28.58172928000001</v>
+        <v>-39.32274346000001</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-28.58172928000001</v>
+        <v>-39.32274346000001</v>
       </c>
       <c r="Q98">
-        <v>-23.68172928000001</v>
+        <v>-34.42274346000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.459094439204298</v>
+        <v>1.930192585605731</v>
       </c>
       <c r="T98">
-        <v>27.54773918364812</v>
+        <v>36.73031891153083</v>
       </c>
       <c r="U98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V98">
         <v>0</v>
       </c>
       <c r="W98">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5036319742844652</v>
+        <v>0.4244560234466908</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.286631777568172</v>
+        <v>0.288531777568172</v>
       </c>
       <c r="C99">
-        <v>-132.857812732076</v>
+        <v>-136.3768246056689</v>
       </c>
       <c r="D99">
-        <v>81.69088726792404</v>
+        <v>81.15897539433115</v>
       </c>
       <c r="E99">
-        <v>283.8387</v>
+        <v>286.8258</v>
       </c>
       <c r="F99">
-        <v>289.7487</v>
+        <v>292.7358</v>
       </c>
       <c r="G99">
         <v>75.2</v>
@@ -9405,28 +9405,28 @@
         <v>29</v>
       </c>
       <c r="M99">
-        <v>68.32274346000001</v>
+        <v>69.02710164000001</v>
       </c>
       <c r="N99">
-        <v>-39.32274346000001</v>
+        <v>-40.02710164000001</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-39.32274346000001</v>
+        <v>-40.02710164000001</v>
       </c>
       <c r="Q99">
-        <v>-34.42274346000001</v>
+        <v>-35.12710164000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.930192585605731</v>
+        <v>2.872388878408596</v>
       </c>
       <c r="T99">
-        <v>36.73031891153083</v>
+        <v>55.09547836729624</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4244560234466908</v>
+        <v>0.4201248395339694</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.288531777568172</v>
+        <v>0.290431777568172</v>
       </c>
       <c r="C100">
-        <v>-136.3768246056689</v>
+        <v>-139.8889544406004</v>
       </c>
       <c r="D100">
-        <v>81.15897539433115</v>
+        <v>80.63394555939966</v>
       </c>
       <c r="E100">
-        <v>286.8258</v>
+        <v>289.8129</v>
       </c>
       <c r="F100">
-        <v>292.7358</v>
+        <v>295.7229</v>
       </c>
       <c r="G100">
         <v>75.2</v>
@@ -9487,28 +9487,28 @@
         <v>29</v>
       </c>
       <c r="M100">
-        <v>69.02710164000001</v>
+        <v>69.73145982000001</v>
       </c>
       <c r="N100">
-        <v>-40.02710164000001</v>
+        <v>-40.73145982000001</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-40.02710164000001</v>
+        <v>-40.73145982000001</v>
       </c>
       <c r="Q100">
-        <v>-35.12710164000001</v>
+        <v>-35.83145982000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.872388878408596</v>
+        <v>5.698977756817192</v>
       </c>
       <c r="T100">
-        <v>55.09547836729624</v>
+        <v>110.1909567345925</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.4201248395339694</v>
+        <v>0.4158811542861515</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.290431777568172</v>
-      </c>
-      <c r="C101">
-        <v>-139.8889544406004</v>
-      </c>
-      <c r="D101">
-        <v>80.63394555939966</v>
-      </c>
-      <c r="E101">
-        <v>289.8129</v>
-      </c>
-      <c r="F101">
-        <v>295.7229</v>
-      </c>
-      <c r="G101">
-        <v>75.2</v>
-      </c>
-      <c r="H101">
-        <v>292.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>33.9</v>
-      </c>
-      <c r="K101">
-        <v>4.899999999999999</v>
-      </c>
-      <c r="L101">
-        <v>29</v>
-      </c>
-      <c r="M101">
-        <v>69.73145982000001</v>
-      </c>
-      <c r="N101">
-        <v>-40.73145982000001</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-40.73145982000001</v>
-      </c>
-      <c r="Q101">
-        <v>-35.83145982000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.698977756817192</v>
-      </c>
-      <c r="T101">
-        <v>110.1909567345925</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4158811542861515</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
